--- a/tinh.xlsx
+++ b/tinh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VKSNDTC\VKS Projects\thongkenhaplieu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VKSNDTC\Projects\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62BC2EEC-6433-47BC-8110-AA140F5FA2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD33C7C-4475-42D9-B629-4D281B5DF22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{8BD0CAC4-3BA0-4DC6-9391-9CBA79D907C0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8BD0CAC4-3BA0-4DC6-9391-9CBA79D907C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -637,9 +637,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33BBBD07-AF56-4FFB-A2BF-B2E8A6A9EBD7}">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="51.65" thickBot="1">
+    <row r="1" spans="1:13" ht="51" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,7 +680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.05" thickTop="1">
+    <row r="2" spans="1:13" ht="18.600000000000001" thickTop="1">
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
@@ -688,43 +688,40 @@
         <v>426</v>
       </c>
       <c r="C2" s="8">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="D2" s="9">
-        <v>201</v>
+        <v>335</v>
       </c>
       <c r="E2" s="10">
-        <f>D2/B2</f>
-        <v>0.47183098591549294</v>
+        <v>0.78638497652582195</v>
       </c>
       <c r="F2" s="7">
         <v>330</v>
       </c>
       <c r="G2" s="11">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="H2" s="12">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="I2" s="13">
-        <f>H2/F2</f>
-        <v>0.39393939393939392</v>
+        <v>0.76060606060606062</v>
       </c>
       <c r="J2" s="7">
         <v>62</v>
       </c>
       <c r="K2" s="12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L2" s="14">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M2" s="5">
-        <f>L2/J2</f>
-        <v>9.6774193548387094E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.350000000000001">
+        <v>0.27419354838709675</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -732,43 +729,40 @@
         <v>378</v>
       </c>
       <c r="C3" s="8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D3" s="9">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E3" s="10">
-        <f t="shared" ref="E3:E35" si="0">D3/B3</f>
-        <v>0.26190476190476192</v>
+        <v>0.30423280423280424</v>
       </c>
       <c r="F3" s="15">
         <v>342</v>
       </c>
       <c r="G3" s="11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H3" s="12">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="I3" s="13">
-        <f t="shared" ref="I3:I35" si="1">H3/F3</f>
-        <v>0.16959064327485379</v>
+        <v>0.28654970760233917</v>
       </c>
       <c r="J3" s="15">
         <v>61</v>
       </c>
       <c r="K3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
-        <f t="shared" ref="M3:M35" si="2">L3/J3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.350000000000001">
+        <v>3.2786885245901641E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="18">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -776,43 +770,40 @@
         <v>188</v>
       </c>
       <c r="C4" s="8">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D4" s="9">
-        <v>99</v>
+        <v>268</v>
       </c>
       <c r="E4" s="10">
-        <f t="shared" si="0"/>
-        <v>0.52659574468085102</v>
+        <v>1.425531914893617</v>
       </c>
       <c r="F4" s="15">
         <v>200</v>
       </c>
       <c r="G4" s="11">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H4" s="12">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="I4" s="13">
-        <f t="shared" si="1"/>
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="J4" s="15">
         <v>17</v>
       </c>
       <c r="K4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18.350000000000001">
+        <v>0.11764705882352941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -820,43 +811,40 @@
         <v>473</v>
       </c>
       <c r="C5" s="8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D5" s="9">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="E5" s="10">
-        <f t="shared" si="0"/>
-        <v>0.19661733615221988</v>
+        <v>0.2452431289640592</v>
       </c>
       <c r="F5" s="15">
         <v>307</v>
       </c>
       <c r="G5" s="11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H5" s="12">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="1"/>
-        <v>0.32247557003257327</v>
+        <v>0.40716612377850164</v>
       </c>
       <c r="J5" s="15">
         <v>26</v>
       </c>
       <c r="K5" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M5" s="5">
-        <f t="shared" si="2"/>
-        <v>0.92307692307692313</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="18.350000000000001">
+        <v>1.0769230769230769</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="18">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -864,43 +852,40 @@
         <v>80</v>
       </c>
       <c r="C6" s="8">
-        <v>12</v>
+        <v>277</v>
       </c>
       <c r="D6" s="9">
-        <v>227</v>
+        <v>504</v>
       </c>
       <c r="E6" s="10">
-        <f t="shared" si="0"/>
-        <v>2.8374999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="F6" s="15">
         <v>77</v>
       </c>
       <c r="G6" s="11">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="H6" s="12">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="I6" s="13">
-        <f t="shared" si="1"/>
-        <v>2.0649350649350651</v>
+        <v>2.8181818181818183</v>
       </c>
       <c r="J6" s="15">
         <v>2</v>
       </c>
       <c r="K6" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18.350000000000001">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18">
       <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
@@ -908,43 +893,40 @@
         <v>430</v>
       </c>
       <c r="C7" s="8">
-        <v>99</v>
+        <v>519</v>
       </c>
       <c r="D7" s="9">
-        <v>721</v>
+        <v>1240</v>
       </c>
       <c r="E7" s="10">
-        <f t="shared" si="0"/>
-        <v>1.6767441860465115</v>
+        <v>2.8837209302325579</v>
       </c>
       <c r="F7" s="15">
         <v>351</v>
       </c>
       <c r="G7" s="11">
-        <v>111</v>
+        <v>936</v>
       </c>
       <c r="H7" s="12">
-        <v>756</v>
+        <v>1692</v>
       </c>
       <c r="I7" s="13">
-        <f t="shared" si="1"/>
-        <v>2.1538461538461537</v>
+        <v>4.8205128205128203</v>
       </c>
       <c r="J7" s="15">
         <v>59</v>
       </c>
       <c r="K7" s="12">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="L7" s="14">
-        <v>119</v>
+        <v>256</v>
       </c>
       <c r="M7" s="5">
-        <f t="shared" si="2"/>
-        <v>2.0169491525423728</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18.350000000000001">
+        <v>4.3389830508474576</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
@@ -952,14 +934,13 @@
         <v>182</v>
       </c>
       <c r="C8" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D8" s="9">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E8" s="10">
-        <f t="shared" si="0"/>
-        <v>0.81868131868131866</v>
+        <v>0.86263736263736268</v>
       </c>
       <c r="F8" s="15">
         <v>180</v>
@@ -968,27 +949,25 @@
         <v>2</v>
       </c>
       <c r="H8" s="12">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="1"/>
-        <v>1.6888888888888889</v>
+        <v>1.7</v>
       </c>
       <c r="J8" s="15">
         <v>40</v>
       </c>
       <c r="K8" s="12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M8" s="5">
-        <f t="shared" si="2"/>
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="18.350000000000001">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="18">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -996,43 +975,40 @@
         <v>66</v>
       </c>
       <c r="C9" s="8">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D9" s="9">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="E9" s="10">
-        <f t="shared" si="0"/>
-        <v>1.2272727272727273</v>
+        <v>1.6212121212121211</v>
       </c>
       <c r="F9" s="15">
         <v>90</v>
       </c>
       <c r="G9" s="11">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H9" s="12">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="I9" s="13">
-        <f t="shared" si="1"/>
-        <v>2.7</v>
+        <v>2.9444444444444446</v>
       </c>
       <c r="J9" s="15">
         <v>3</v>
       </c>
       <c r="K9" s="12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L9" s="14">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="2"/>
-        <v>12.666666666666666</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18.350000000000001">
+        <v>12.333333333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18">
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
@@ -1040,43 +1016,40 @@
         <v>457</v>
       </c>
       <c r="C10" s="8">
-        <v>39</v>
+        <v>346</v>
       </c>
       <c r="D10" s="9">
-        <v>457</v>
+        <v>803</v>
       </c>
       <c r="E10" s="10">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.7571115973741793</v>
       </c>
       <c r="F10" s="15">
         <v>410</v>
       </c>
       <c r="G10" s="11">
-        <v>62</v>
+        <v>982</v>
       </c>
       <c r="H10" s="12">
-        <v>553</v>
+        <v>1535</v>
       </c>
       <c r="I10" s="13">
-        <f t="shared" si="1"/>
-        <v>1.3487804878048781</v>
+        <v>3.7439024390243905</v>
       </c>
       <c r="J10" s="15">
         <v>76</v>
       </c>
       <c r="K10" s="12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L10" s="14">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="M10" s="5">
-        <f t="shared" si="2"/>
-        <v>0.31578947368421051</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="18.350000000000001">
+        <v>0.46052631578947367</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="18">
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
@@ -1084,43 +1057,40 @@
         <v>222</v>
       </c>
       <c r="C11" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D11" s="9">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E11" s="10">
-        <f t="shared" si="0"/>
-        <v>0.3783783783783784</v>
+        <v>0.40540540540540543</v>
       </c>
       <c r="F11" s="15">
         <v>263</v>
       </c>
       <c r="G11" s="11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H11" s="12">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="I11" s="13">
-        <f t="shared" si="1"/>
-        <v>0.47148288973384028</v>
+        <v>0.63117870722433456</v>
       </c>
       <c r="J11" s="15">
         <v>4</v>
       </c>
       <c r="K11" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M11" s="5">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18.350000000000001">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18">
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
@@ -1128,43 +1098,40 @@
         <v>287</v>
       </c>
       <c r="C12" s="8">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="D12" s="9">
-        <v>193</v>
+        <v>501</v>
       </c>
       <c r="E12" s="10">
-        <f t="shared" si="0"/>
-        <v>0.67247386759581884</v>
+        <v>1.745644599303136</v>
       </c>
       <c r="F12" s="15">
         <v>340</v>
       </c>
       <c r="G12" s="11">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="H12" s="12">
-        <v>446</v>
+        <v>568</v>
       </c>
       <c r="I12" s="13">
-        <f t="shared" si="1"/>
-        <v>1.3117647058823529</v>
+        <v>1.6705882352941177</v>
       </c>
       <c r="J12" s="15">
         <v>41</v>
       </c>
       <c r="K12" s="12">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L12" s="14">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="M12" s="5">
-        <f t="shared" si="2"/>
-        <v>0.80487804878048785</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="18.350000000000001">
+        <v>3.1463414634146343</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="18">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
@@ -1172,43 +1139,40 @@
         <v>2967</v>
       </c>
       <c r="C13" s="8">
-        <v>103</v>
+        <v>729</v>
       </c>
       <c r="D13" s="9">
-        <v>1099</v>
+        <v>1828</v>
       </c>
       <c r="E13" s="10">
-        <f t="shared" si="0"/>
-        <v>0.37040781934614087</v>
+        <v>0.61611054937647458</v>
       </c>
       <c r="F13" s="15">
         <v>1226</v>
       </c>
       <c r="G13" s="11">
-        <v>62</v>
+        <v>665</v>
       </c>
       <c r="H13" s="12">
-        <v>1192</v>
+        <v>1857</v>
       </c>
       <c r="I13" s="13">
-        <f t="shared" si="1"/>
-        <v>0.97226753670473087</v>
+        <v>1.5146818923327896</v>
       </c>
       <c r="J13" s="15">
         <v>237</v>
       </c>
       <c r="K13" s="12">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="L13" s="14">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="M13" s="5">
-        <f t="shared" si="2"/>
-        <v>0.22362869198312235</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="18.350000000000001">
+        <v>6.7510548523206745E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
@@ -1216,43 +1180,40 @@
         <v>121</v>
       </c>
       <c r="C14" s="8">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D14" s="9">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E14" s="10">
-        <f t="shared" si="0"/>
-        <v>5.7851239669421489E-2</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="F14" s="15">
         <v>123</v>
       </c>
       <c r="G14" s="11">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H14" s="12">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="1"/>
-        <v>0.86178861788617889</v>
+        <v>1.089430894308943</v>
       </c>
       <c r="J14" s="15">
         <v>12</v>
       </c>
       <c r="K14" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M14" s="5">
-        <f t="shared" si="2"/>
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="18.350000000000001">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="18">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
@@ -1260,43 +1221,40 @@
         <v>504</v>
       </c>
       <c r="C15" s="8">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="D15" s="9">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="E15" s="10">
-        <f t="shared" si="0"/>
-        <v>0.33730158730158732</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="F15" s="15">
         <v>397</v>
       </c>
       <c r="G15" s="11">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="H15" s="12">
-        <v>511</v>
+        <v>643</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="1"/>
-        <v>1.2871536523929472</v>
+        <v>1.619647355163728</v>
       </c>
       <c r="J15" s="15">
         <v>59</v>
       </c>
       <c r="K15" s="12">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="L15" s="14">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5">
-        <f t="shared" si="2"/>
-        <v>1.1694915254237288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="18.350000000000001">
+        <v>0.15254237288135594</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="18">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -1304,43 +1262,40 @@
         <v>53</v>
       </c>
       <c r="C16" s="8">
-        <v>38</v>
+        <v>183</v>
       </c>
       <c r="D16" s="9">
-        <v>410</v>
+        <v>593</v>
       </c>
       <c r="E16" s="10">
-        <f t="shared" si="0"/>
-        <v>7.7358490566037732</v>
+        <v>11.188679245283019</v>
       </c>
       <c r="F16" s="15">
         <v>105</v>
       </c>
       <c r="G16" s="11">
-        <v>19</v>
+        <v>272</v>
       </c>
       <c r="H16" s="12">
-        <v>371</v>
+        <v>643</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="1"/>
-        <v>3.5333333333333332</v>
+        <v>6.1238095238095234</v>
       </c>
       <c r="J16" s="15">
         <v>22</v>
       </c>
       <c r="K16" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M16" s="5">
-        <f t="shared" si="2"/>
-        <v>0.31818181818181818</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="18.350000000000001">
+        <v>1.6363636363636365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="18">
       <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
@@ -1348,43 +1303,40 @@
         <v>154</v>
       </c>
       <c r="C17" s="8">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D17" s="9">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="E17" s="10">
-        <f t="shared" si="0"/>
-        <v>0.87662337662337664</v>
+        <v>1.1493506493506493</v>
       </c>
       <c r="F17" s="15">
         <v>190</v>
       </c>
       <c r="G17" s="11">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H17" s="12">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="I17" s="13">
-        <f t="shared" si="1"/>
-        <v>0.70526315789473681</v>
+        <v>1.1105263157894736</v>
       </c>
       <c r="J17" s="15">
         <v>23</v>
       </c>
       <c r="K17" s="12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L17" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M17" s="5">
-        <f t="shared" si="2"/>
-        <v>1.2173913043478262</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="18.350000000000001">
+        <v>0.52173913043478259</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="18">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
@@ -1392,27 +1344,25 @@
         <v>355</v>
       </c>
       <c r="C18" s="8">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D18" s="9">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="E18" s="10">
-        <f t="shared" si="0"/>
-        <v>0.74647887323943662</v>
+        <v>0.87605633802816907</v>
       </c>
       <c r="F18" s="15">
         <v>176</v>
       </c>
       <c r="G18" s="11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="12">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I18" s="13">
-        <f t="shared" si="1"/>
-        <v>0.81818181818181823</v>
+        <v>0.84090909090909094</v>
       </c>
       <c r="J18" s="15">
         <v>30</v>
@@ -1421,14 +1371,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M18" s="5">
-        <f t="shared" si="2"/>
-        <v>0.43333333333333335</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="18.350000000000001">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="18">
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
@@ -1436,43 +1385,40 @@
         <v>47</v>
       </c>
       <c r="C19" s="8">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D19" s="9">
-        <v>381</v>
+        <v>430</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="0"/>
-        <v>8.1063829787234045</v>
+        <v>9.1489361702127656</v>
       </c>
       <c r="F19" s="15">
         <v>35</v>
       </c>
       <c r="G19" s="11">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H19" s="12">
         <v>316</v>
       </c>
       <c r="I19" s="13">
-        <f t="shared" si="1"/>
         <v>9.0285714285714285</v>
       </c>
       <c r="J19" s="15">
         <v>2</v>
       </c>
       <c r="K19" s="12">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="L19" s="14">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="M19" s="5">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="18.350000000000001">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18">
       <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
@@ -1486,37 +1432,34 @@
         <v>66</v>
       </c>
       <c r="E20" s="10">
-        <f t="shared" si="0"/>
         <v>6.8393782383419685E-2</v>
       </c>
       <c r="F20" s="15">
         <v>241</v>
       </c>
       <c r="G20" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="12">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I20" s="13">
-        <f t="shared" si="1"/>
-        <v>0.77593360995850624</v>
+        <v>0.78838174273858919</v>
       </c>
       <c r="J20" s="15">
         <v>32</v>
       </c>
       <c r="K20" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
         <v>2</v>
       </c>
       <c r="M20" s="5">
-        <f t="shared" si="2"/>
-        <v>6.25E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="18.350000000000001">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18">
       <c r="A21" s="6" t="s">
         <v>24</v>
       </c>
@@ -1524,27 +1467,25 @@
         <v>98</v>
       </c>
       <c r="C21" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D21" s="9">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" si="0"/>
-        <v>1.6734693877551021</v>
+        <v>1.7653061224489797</v>
       </c>
       <c r="F21" s="15">
         <v>160</v>
       </c>
       <c r="G21" s="11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H21" s="12">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="I21" s="13">
-        <f t="shared" si="1"/>
-        <v>0.93125000000000002</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="J21" s="15">
         <v>3</v>
@@ -1553,14 +1494,13 @@
         <v>1</v>
       </c>
       <c r="L21" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M21" s="5">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18.350000000000001">
+        <v>9.3333333333333339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18">
       <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
@@ -1568,27 +1508,25 @@
         <v>147</v>
       </c>
       <c r="C22" s="8">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D22" s="9">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="0"/>
-        <v>1.1972789115646258</v>
+        <v>1.6190476190476191</v>
       </c>
       <c r="F22" s="15">
         <v>73</v>
       </c>
       <c r="G22" s="11">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="H22" s="12">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" si="1"/>
-        <v>1.8356164383561644</v>
+        <v>1.8082191780821917</v>
       </c>
       <c r="J22" s="15">
         <v>10</v>
@@ -1600,11 +1538,10 @@
         <v>28</v>
       </c>
       <c r="M22" s="5">
-        <f t="shared" si="2"/>
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="18.350000000000001">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="18">
       <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
@@ -1612,43 +1549,40 @@
         <v>291</v>
       </c>
       <c r="C23" s="8">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="D23" s="9">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="0"/>
-        <v>0.35738831615120276</v>
+        <v>0.60481099656357384</v>
       </c>
       <c r="F23" s="15">
         <v>211</v>
       </c>
       <c r="G23" s="11">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H23" s="12">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="I23" s="13">
-        <f t="shared" si="1"/>
-        <v>0.59715639810426535</v>
+        <v>0.80094786729857825</v>
       </c>
       <c r="J23" s="15">
         <v>32</v>
       </c>
       <c r="K23" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L23" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M23" s="5">
-        <f t="shared" si="2"/>
-        <v>0.9375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="18.350000000000001">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="18">
       <c r="A24" s="6" t="s">
         <v>27</v>
       </c>
@@ -1656,27 +1590,25 @@
         <v>369</v>
       </c>
       <c r="C24" s="8">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="D24" s="9">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="E24" s="10">
-        <f t="shared" si="0"/>
-        <v>0.3143631436314363</v>
+        <v>0.47154471544715448</v>
       </c>
       <c r="F24" s="15">
         <v>175</v>
       </c>
       <c r="G24" s="11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H24" s="12">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="I24" s="13">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.78285714285714281</v>
       </c>
       <c r="J24" s="15">
         <v>22</v>
@@ -1688,11 +1620,10 @@
         <v>18</v>
       </c>
       <c r="M24" s="5">
-        <f t="shared" si="2"/>
-        <v>0.81818181818181823</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="18.350000000000001">
+        <v>2.2272727272727271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="18">
       <c r="A25" s="6" t="s">
         <v>28</v>
       </c>
@@ -1700,43 +1631,40 @@
         <v>261</v>
       </c>
       <c r="C25" s="8">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D25" s="9">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="0"/>
-        <v>0.33716475095785442</v>
+        <v>0.66283524904214564</v>
       </c>
       <c r="F25" s="15">
         <v>306</v>
       </c>
       <c r="G25" s="11">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H25" s="12">
-        <v>217</v>
+        <v>293</v>
       </c>
       <c r="I25" s="13">
-        <f t="shared" si="1"/>
-        <v>0.70915032679738566</v>
+        <v>0.95751633986928109</v>
       </c>
       <c r="J25" s="15">
         <v>18</v>
       </c>
       <c r="K25" s="12">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L25" s="14">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" si="2"/>
-        <v>2.1111111111111112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="18.350000000000001">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="18">
       <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
@@ -1744,27 +1672,25 @@
         <v>168</v>
       </c>
       <c r="C26" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D26" s="9">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" si="0"/>
-        <v>0.97619047619047616</v>
+        <v>1.0238095238095237</v>
       </c>
       <c r="F26" s="15">
         <v>172</v>
       </c>
       <c r="G26" s="11">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H26" s="12">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I26" s="13">
-        <f t="shared" si="1"/>
-        <v>1.4244186046511629</v>
+        <v>1.4476744186046511</v>
       </c>
       <c r="J26" s="15">
         <v>31</v>
@@ -1773,14 +1699,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M26" s="5">
-        <f t="shared" si="2"/>
-        <v>0.5161290322580645</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="18.350000000000001">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="18">
       <c r="A27" s="6" t="s">
         <v>30</v>
       </c>
@@ -1788,43 +1713,40 @@
         <v>1951</v>
       </c>
       <c r="C27" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D27" s="9">
-        <v>1979</v>
+        <v>1992</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="0"/>
-        <v>1.0143516145566376</v>
+        <v>1.0210148641722194</v>
       </c>
       <c r="F27" s="15">
         <v>1908</v>
       </c>
       <c r="G27" s="11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="12">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="I27" s="13">
-        <f t="shared" si="1"/>
-        <v>1.0031446540880504</v>
+        <v>1.0052410901467506</v>
       </c>
       <c r="J27" s="15">
         <v>463</v>
       </c>
       <c r="K27" s="12">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="L27" s="14">
-        <v>502</v>
+        <v>558</v>
       </c>
       <c r="M27" s="5">
-        <f t="shared" si="2"/>
-        <v>1.0842332613390928</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="18.350000000000001">
+        <v>4.5356371490280781E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="18">
       <c r="A28" s="6" t="s">
         <v>31</v>
       </c>
@@ -1832,43 +1754,40 @@
         <v>125</v>
       </c>
       <c r="C28" s="8">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D28" s="9">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="0"/>
-        <v>1.1279999999999999</v>
+        <v>1.232</v>
       </c>
       <c r="F28" s="15">
         <v>210</v>
       </c>
       <c r="G28" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12">
         <v>233</v>
       </c>
       <c r="I28" s="13">
-        <f t="shared" si="1"/>
         <v>1.1095238095238096</v>
       </c>
       <c r="J28" s="15">
         <v>17</v>
       </c>
       <c r="K28" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M28" s="5">
-        <f t="shared" si="2"/>
-        <v>1.1176470588235294</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="18.350000000000001">
+        <v>6.1764705882352944</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="18">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -1876,43 +1795,40 @@
         <v>80</v>
       </c>
       <c r="C29" s="8">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D29" s="9">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="0"/>
-        <v>0.86250000000000004</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F29" s="15">
         <v>126</v>
       </c>
       <c r="G29" s="11">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="H29" s="12">
-        <v>119</v>
+        <v>274</v>
       </c>
       <c r="I29" s="13">
-        <f t="shared" si="1"/>
-        <v>0.94444444444444442</v>
+        <v>2.1746031746031744</v>
       </c>
       <c r="J29" s="15">
         <v>2</v>
       </c>
       <c r="K29" s="12">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L29" s="14">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="M29" s="5">
-        <f t="shared" si="2"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="18.350000000000001">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="18">
       <c r="A30" s="6" t="s">
         <v>33</v>
       </c>
@@ -1920,43 +1836,40 @@
         <v>179</v>
       </c>
       <c r="C30" s="8">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="D30" s="9">
-        <v>427</v>
+        <v>628</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="0"/>
-        <v>2.3854748603351954</v>
+        <v>3.5083798882681565</v>
       </c>
       <c r="F30" s="15">
         <v>233</v>
       </c>
       <c r="G30" s="11">
-        <v>9</v>
+        <v>317</v>
       </c>
       <c r="H30" s="12">
-        <v>325</v>
+        <v>642</v>
       </c>
       <c r="I30" s="13">
-        <f t="shared" si="1"/>
-        <v>1.3948497854077253</v>
+        <v>2.755364806866953</v>
       </c>
       <c r="J30" s="15">
         <v>34</v>
       </c>
       <c r="K30" s="12">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L30" s="14">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M30" s="5">
-        <f t="shared" si="2"/>
-        <v>0.3235294117647059</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="18.350000000000001">
+        <v>0.61764705882352944</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="18">
       <c r="A31" s="6" t="s">
         <v>34</v>
       </c>
@@ -1964,43 +1877,40 @@
         <v>235</v>
       </c>
       <c r="C31" s="8">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D31" s="9">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="E31" s="10">
-        <f t="shared" si="0"/>
-        <v>0.22553191489361701</v>
+        <v>0.38723404255319149</v>
       </c>
       <c r="F31" s="15">
         <v>173</v>
       </c>
       <c r="G31" s="11">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="H31" s="12">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="I31" s="13">
-        <f t="shared" si="1"/>
-        <v>0.80924855491329484</v>
+        <v>1.046242774566474</v>
       </c>
       <c r="J31" s="15">
         <v>5</v>
       </c>
       <c r="K31" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M31" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="18.350000000000001">
+        <v>66.599999999999994</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="18">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -2008,43 +1918,40 @@
         <v>121</v>
       </c>
       <c r="C32" s="8">
-        <v>31</v>
+        <v>352</v>
       </c>
       <c r="D32" s="9">
-        <v>697</v>
+        <v>1049</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="0"/>
-        <v>5.7603305785123968</v>
+        <v>8.6694214876033051</v>
       </c>
       <c r="F32" s="15">
         <v>293</v>
       </c>
       <c r="G32" s="11">
-        <v>47</v>
+        <v>964</v>
       </c>
       <c r="H32" s="12">
-        <v>1000</v>
+        <v>1964</v>
       </c>
       <c r="I32" s="13">
-        <f t="shared" si="1"/>
-        <v>3.4129692832764507</v>
+        <v>6.7030716723549491</v>
       </c>
       <c r="J32" s="15">
         <v>27</v>
       </c>
       <c r="K32" s="12">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="L32" s="14">
-        <v>225</v>
+        <v>333</v>
       </c>
       <c r="M32" s="5">
-        <f t="shared" si="2"/>
-        <v>8.3333333333333339</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="18.350000000000001">
+        <v>1.7407407407407407</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="18">
       <c r="A33" s="6" t="s">
         <v>36</v>
       </c>
@@ -2052,43 +1959,40 @@
         <v>96</v>
       </c>
       <c r="C33" s="8">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="D33" s="9">
-        <v>286</v>
+        <v>373</v>
       </c>
       <c r="E33" s="10">
-        <f t="shared" si="0"/>
-        <v>2.9791666666666665</v>
+        <v>3.8854166666666665</v>
       </c>
       <c r="F33" s="15">
         <v>57</v>
       </c>
       <c r="G33" s="11">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="H33" s="12">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="I33" s="13">
-        <f t="shared" si="1"/>
-        <v>2.8771929824561404</v>
+        <v>4.7543859649122808</v>
       </c>
       <c r="J33" s="15">
         <v>2</v>
       </c>
       <c r="K33" s="12">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L33" s="14">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M33" s="5">
-        <f t="shared" si="2"/>
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="18.350000000000001">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="18">
       <c r="A34" s="6" t="s">
         <v>37</v>
       </c>
@@ -2096,43 +2000,40 @@
         <v>120</v>
       </c>
       <c r="C34" s="8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D34" s="9">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E34" s="10">
-        <f t="shared" si="0"/>
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F34" s="15">
         <v>123</v>
       </c>
       <c r="G34" s="11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H34" s="12">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I34" s="13">
-        <f t="shared" si="1"/>
-        <v>0.81300813008130079</v>
+        <v>0.87804878048780488</v>
       </c>
       <c r="J34" s="15">
         <v>2</v>
       </c>
       <c r="K34" s="12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M34" s="5">
-        <f t="shared" si="2"/>
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="19.05" thickBot="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="18.600000000000001" thickBot="1">
       <c r="A35" s="6" t="s">
         <v>38</v>
       </c>
@@ -2140,43 +2041,40 @@
         <v>179</v>
       </c>
       <c r="C35" s="8">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D35" s="9">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="E35" s="10">
-        <f t="shared" si="0"/>
-        <v>1.0726256983240223</v>
+        <v>1.2458100558659218</v>
       </c>
       <c r="F35" s="16">
         <v>179</v>
       </c>
       <c r="G35" s="11">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H35" s="12">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="I35" s="13">
-        <f t="shared" si="1"/>
-        <v>1.1955307262569832</v>
+        <v>1.2849162011173185</v>
       </c>
       <c r="J35" s="16">
         <v>20</v>
       </c>
       <c r="K35" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M35" s="5">
-        <f t="shared" si="2"/>
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="14.95" thickTop="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15" thickTop="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tinh.xlsx
+++ b/tinh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VKSNDTC\Projects\thongkenhaplieu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD33C7C-4475-42D9-B629-4D281B5DF22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEFB753-D837-4DE7-BF74-D104846B343E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8BD0CAC4-3BA0-4DC6-9391-9CBA79D907C0}"/>
+    <workbookView xWindow="27636" yWindow="1488" windowWidth="17280" windowHeight="8880" xr2:uid="{8BD0CAC4-3BA0-4DC6-9391-9CBA79D907C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -638,6 +638,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33BBBD07-AF56-4FFB-A2BF-B2E8A6A9EBD7}">
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="51" thickBot="1">
       <c r="A1" s="1" t="s">
@@ -1716,7 +1719,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="9">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="E27" s="10">
         <v>1.0210148641722194</v>

--- a/tinh.xlsx
+++ b/tinh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEFB753-D837-4DE7-BF74-D104846B343E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1F5A8A-3D29-4264-ADF6-069841724708}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="27636" yWindow="1488" windowWidth="17280" windowHeight="8880" xr2:uid="{8BD0CAC4-3BA0-4DC6-9391-9CBA79D907C0}"/>
   </bookViews>
@@ -1719,7 +1719,7 @@
         <v>13</v>
       </c>
       <c r="D27" s="9">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="E27" s="10">
         <v>1.0210148641722194</v>

--- a/tinh.xlsx
+++ b/tinh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BCC95B-89A6-492B-B345-F300725FB3AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD264C00-E2D5-46E2-B74E-919FF41363AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-84" windowWidth="23256" windowHeight="12456" xr2:uid="{0B4F58B4-2F58-4950-9789-4E40BB9171AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B4F58B4-2F58-4950-9789-4E40BB9171AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1664,7 +1664,7 @@
         <v>31</v>
       </c>
       <c r="K26" s="13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14">
         <v>14</v>
@@ -1693,7 +1693,7 @@
         <v>1908</v>
       </c>
       <c r="G27" s="10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="11">
         <v>1917</v>

--- a/tinh.xlsx
+++ b/tinh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD264C00-E2D5-46E2-B74E-919FF41363AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4885A7F-A872-4182-A4F8-BCD8894DCA71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B4F58B4-2F58-4950-9789-4E40BB9171AB}"/>
   </bookViews>
@@ -248,7 +248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -282,13 +282,16 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,16 +679,16 @@
       <c r="I2" s="12">
         <v>0.82727272727272727</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="14">
         <v>62</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="15">
         <v>5</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="16">
         <v>22</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="13">
         <v>0.35483870967741937</v>
       </c>
     </row>
@@ -717,16 +720,16 @@
       <c r="I3" s="12">
         <v>0.32456140350877194</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="14">
         <v>61</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="15">
         <v>3</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="16">
         <v>5</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="13">
         <v>8.1967213114754092E-2</v>
       </c>
     </row>
@@ -758,16 +761,16 @@
       <c r="I4" s="12">
         <v>1.0049999999999999</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="14">
         <v>17</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="15">
         <v>2</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="16">
         <v>4</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="13">
         <v>0.23529411764705882</v>
       </c>
     </row>
@@ -799,16 +802,16 @@
       <c r="I5" s="12">
         <v>0.44951140065146578</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="14">
         <v>26</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="15">
         <v>1</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="16">
         <v>29</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="13">
         <v>1.1153846153846154</v>
       </c>
     </row>
@@ -840,16 +843,16 @@
       <c r="I6" s="12">
         <v>3.168831168831169</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="14">
         <v>2</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="15">
         <v>0</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="16">
         <v>1</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="13">
         <v>0.5</v>
       </c>
     </row>
@@ -881,16 +884,16 @@
       <c r="I7" s="12">
         <v>5.3532763532763532</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="14">
         <v>59</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="15">
         <v>50</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="16">
         <v>306</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="13">
         <v>5.1864406779661021</v>
       </c>
     </row>
@@ -922,16 +925,16 @@
       <c r="I8" s="12">
         <v>1.8055555555555556</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="14">
         <v>40</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="15">
         <v>1</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="16">
         <v>31</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="13">
         <v>0.77500000000000002</v>
       </c>
     </row>
@@ -963,16 +966,16 @@
       <c r="I9" s="12">
         <v>3.0333333333333332</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="14">
         <v>3</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="15">
         <v>4</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="16">
         <v>41</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="13">
         <v>13.666666666666666</v>
       </c>
     </row>
@@ -1004,16 +1007,16 @@
       <c r="I10" s="12">
         <v>4.9487804878048784</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="14">
         <v>76</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="15">
         <v>4</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="16">
         <v>39</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="13">
         <v>0.51315789473684215</v>
       </c>
     </row>
@@ -1045,16 +1048,16 @@
       <c r="I11" s="12">
         <v>0.63117870722433456</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="14">
         <v>4</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="15">
         <v>0</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="16">
         <v>10</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="13">
         <v>2.5</v>
       </c>
     </row>
@@ -1086,16 +1089,16 @@
       <c r="I12" s="12">
         <v>1.9205882352941177</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="14">
         <v>41</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="15">
         <v>18</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="16">
         <v>65</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="13">
         <v>1.5853658536585367</v>
       </c>
     </row>
@@ -1127,16 +1130,16 @@
       <c r="I13" s="12">
         <v>1.5522022838499185</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="14">
         <v>237</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="15">
         <v>4</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="16">
         <v>133</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="13">
         <v>0.56118143459915615</v>
       </c>
     </row>
@@ -1168,16 +1171,16 @@
       <c r="I14" s="12">
         <v>1.5040650406504066</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="14">
         <v>12</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="16">
         <v>16</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="13">
         <v>1.3333333333333333</v>
       </c>
     </row>
@@ -1209,16 +1212,16 @@
       <c r="I15" s="12">
         <v>2.0176322418136019</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="14">
         <v>59</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="15">
         <v>47</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="16">
         <v>155</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="13">
         <v>2.6271186440677967</v>
       </c>
     </row>
@@ -1250,16 +1253,16 @@
       <c r="I16" s="12">
         <v>6.2</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="14">
         <v>22</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="16">
         <v>9</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="13">
         <v>0.40909090909090912</v>
       </c>
     </row>
@@ -1291,16 +1294,16 @@
       <c r="I17" s="12">
         <v>1.3263157894736841</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="14">
         <v>23</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="15">
         <v>1</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="16">
         <v>37</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17" s="13">
         <v>1.6086956521739131</v>
       </c>
     </row>
@@ -1332,16 +1335,16 @@
       <c r="I18" s="12">
         <v>0.875</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="14">
         <v>30</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="15">
         <v>2</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="16">
         <v>14</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18" s="13">
         <v>0.46666666666666667</v>
       </c>
     </row>
@@ -1373,16 +1376,16 @@
       <c r="I19" s="12">
         <v>9.1714285714285708</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="14">
         <v>2</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="15">
         <v>6</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="16">
         <v>72</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="13">
         <v>36</v>
       </c>
     </row>
@@ -1414,16 +1417,16 @@
       <c r="I20" s="12">
         <v>0.80497925311203322</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="14">
         <v>32</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="15">
         <v>0</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="16">
         <v>2</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="13">
         <v>6.25E-2</v>
       </c>
     </row>
@@ -1455,16 +1458,16 @@
       <c r="I21" s="12">
         <v>1.14375</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="14">
         <v>3</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="15">
         <v>4</v>
       </c>
-      <c r="L21" s="14">
+      <c r="L21" s="16">
         <v>20</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21" s="13">
         <v>6.666666666666667</v>
       </c>
     </row>
@@ -1496,16 +1499,16 @@
       <c r="I22" s="12">
         <v>1.8630136986301369</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="14">
         <v>10</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="15">
         <v>1</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="16">
         <v>29</v>
       </c>
-      <c r="M22" s="15">
+      <c r="M22" s="13">
         <v>2.9</v>
       </c>
     </row>
@@ -1537,16 +1540,16 @@
       <c r="I23" s="12">
         <v>0.89573459715639814</v>
       </c>
-      <c r="J23" s="7">
+      <c r="J23" s="14">
         <v>32</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="15">
         <v>5</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="16">
         <v>43</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23" s="13">
         <v>1.34375</v>
       </c>
     </row>
@@ -1578,16 +1581,16 @@
       <c r="I24" s="12">
         <v>0.80571428571428572</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="14">
         <v>22</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="15">
         <v>3</v>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="16">
         <v>21</v>
       </c>
-      <c r="M24" s="15">
+      <c r="M24" s="13">
         <v>0.95454545454545459</v>
       </c>
     </row>
@@ -1619,16 +1622,16 @@
       <c r="I25" s="12">
         <v>0.98692810457516345</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="14">
         <v>18</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="15">
         <v>3</v>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="16">
         <v>52</v>
       </c>
-      <c r="M25" s="15">
+      <c r="M25" s="13">
         <v>2.8888888888888888</v>
       </c>
     </row>
@@ -1660,16 +1663,16 @@
       <c r="I26" s="12">
         <v>1.4651162790697674</v>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="14">
         <v>31</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="15">
         <v>0</v>
       </c>
-      <c r="L26" s="14">
+      <c r="L26" s="16">
         <v>14</v>
       </c>
-      <c r="M26" s="15">
+      <c r="M26" s="13">
         <v>0.45161290322580644</v>
       </c>
     </row>
@@ -1701,16 +1704,16 @@
       <c r="I27" s="12">
         <v>1.0047169811320755</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="14">
         <v>463</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="15">
         <v>1</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="16">
         <v>559</v>
       </c>
-      <c r="M27" s="15">
+      <c r="M27" s="13">
         <v>1.2073434125269979</v>
       </c>
     </row>
@@ -1742,16 +1745,16 @@
       <c r="I28" s="12">
         <v>1.1333333333333333</v>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="14">
         <v>17</v>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="15">
         <v>3</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="16">
         <v>24</v>
       </c>
-      <c r="M28" s="15">
+      <c r="M28" s="13">
         <v>1.411764705882353</v>
       </c>
     </row>
@@ -1783,16 +1786,16 @@
       <c r="I29" s="12">
         <v>2.3492063492063493</v>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="14">
         <v>2</v>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="15">
         <v>11</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="16">
         <v>116</v>
       </c>
-      <c r="M29" s="15">
+      <c r="M29" s="13">
         <v>58</v>
       </c>
     </row>
@@ -1824,16 +1827,16 @@
       <c r="I30" s="12">
         <v>3.1759656652360513</v>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="14">
         <v>34</v>
       </c>
-      <c r="K30" s="13">
+      <c r="K30" s="15">
         <v>4</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="16">
         <v>27</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30" s="13">
         <v>0.79411764705882348</v>
       </c>
     </row>
@@ -1865,16 +1868,16 @@
       <c r="I31" s="12">
         <v>1.4104046242774566</v>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="14">
         <v>5</v>
       </c>
-      <c r="K31" s="13">
+      <c r="K31" s="15">
         <v>2</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="16">
         <v>23</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="13">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -1906,16 +1909,16 @@
       <c r="I32" s="12">
         <v>7.197952218430034</v>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="14">
         <v>27</v>
       </c>
-      <c r="K32" s="13">
+      <c r="K32" s="15">
         <v>64</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L32" s="16">
         <v>397</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="13">
         <v>14.703703703703704</v>
       </c>
     </row>
@@ -1947,16 +1950,16 @@
       <c r="I33" s="12">
         <v>5.807017543859649</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J33" s="14">
         <v>2</v>
       </c>
-      <c r="K33" s="13">
+      <c r="K33" s="15">
         <v>4</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="16">
         <v>51</v>
       </c>
-      <c r="M33" s="15">
+      <c r="M33" s="13">
         <v>25.5</v>
       </c>
     </row>
@@ -1988,16 +1991,16 @@
       <c r="I34" s="12">
         <v>0.92682926829268297</v>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="14">
         <v>2</v>
       </c>
-      <c r="K34" s="13">
+      <c r="K34" s="15">
         <v>0</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="16">
         <v>36</v>
       </c>
-      <c r="M34" s="15">
+      <c r="M34" s="13">
         <v>18</v>
       </c>
     </row>
@@ -2029,16 +2032,16 @@
       <c r="I35" s="12">
         <v>1.5139664804469273</v>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="14">
         <v>20</v>
       </c>
-      <c r="K35" s="13">
+      <c r="K35" s="15">
         <v>6</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L35" s="16">
         <v>43</v>
       </c>
-      <c r="M35" s="15">
+      <c r="M35" s="13">
         <v>2.15</v>
       </c>
     </row>

--- a/tinh.xlsx
+++ b/tinh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4885A7F-A872-4182-A4F8-BCD8894DCA71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43A3F9D-5001-4FB6-8744-5D7792910F53}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B4F58B4-2F58-4950-9789-4E40BB9171AB}"/>
   </bookViews>
@@ -248,7 +248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -264,20 +264,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -292,6 +280,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,40 +652,40 @@
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="10">
         <v>426</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="10">
         <v>78</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="13">
         <v>413</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>0.96948356807511737</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="10">
         <v>330</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="14">
         <v>22</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="15">
         <v>273</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="8">
         <v>0.82727272727272727</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="10">
         <v>62</v>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="11">
         <v>5</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="12">
         <v>22</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="9">
         <v>0.35483870967741937</v>
       </c>
     </row>
@@ -696,40 +693,40 @@
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="10">
         <v>378</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="10">
         <v>38</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="13">
         <v>153</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="7">
         <v>0.40476190476190477</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="10">
         <v>342</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="14">
         <v>13</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="15">
         <v>111</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>0.32456140350877194</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="10">
         <v>61</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="11">
         <v>3</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="12">
         <v>5</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="9">
         <v>8.1967213114754092E-2</v>
       </c>
     </row>
@@ -737,40 +734,40 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="10">
         <v>188</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="10">
         <v>91</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="13">
         <v>359</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="7">
         <v>1.9095744680851063</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="10">
         <v>200</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="14">
         <v>65</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="15">
         <v>201</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="8">
         <v>1.0049999999999999</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="10">
         <v>17</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="11">
         <v>2</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="12">
         <v>4</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="9">
         <v>0.23529411764705882</v>
       </c>
     </row>
@@ -778,40 +775,40 @@
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>473</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="10">
         <v>13</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="13">
         <v>129</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>0.27272727272727271</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="10">
         <v>307</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="14">
         <v>13</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="15">
         <v>138</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>0.44951140065146578</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>26</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="11">
         <v>1</v>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="12">
         <v>29</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="9">
         <v>1.1153846153846154</v>
       </c>
     </row>
@@ -819,40 +816,40 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>80</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="10">
         <v>96</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="13">
         <v>600</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>7.5</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="10">
         <v>77</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="14">
         <v>27</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="15">
         <v>244</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>3.168831168831169</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>2</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="11">
         <v>0</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="12">
         <v>1</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="9">
         <v>0.5</v>
       </c>
     </row>
@@ -860,40 +857,40 @@
       <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>430</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="10">
         <v>116</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="13">
         <v>1356</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>3.1534883720930234</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="10">
         <v>351</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="14">
         <v>187</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="15">
         <v>1879</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="8">
         <v>5.3532763532763532</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="10">
         <v>59</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="11">
         <v>50</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="12">
         <v>306</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="9">
         <v>5.1864406779661021</v>
       </c>
     </row>
@@ -901,40 +898,40 @@
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>182</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="10">
         <v>10</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="13">
         <v>167</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <v>0.91758241758241754</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="10">
         <v>180</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="14">
         <v>19</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="15">
         <v>325</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>1.8055555555555556</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="10">
         <v>40</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="11">
         <v>1</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="12">
         <v>31</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="9">
         <v>0.77500000000000002</v>
       </c>
     </row>
@@ -942,40 +939,40 @@
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>66</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="10">
         <v>12</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="13">
         <v>119</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>1.803030303030303</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="10">
         <v>90</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="14">
         <v>8</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="15">
         <v>273</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="8">
         <v>3.0333333333333332</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="10">
         <v>3</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="11">
         <v>4</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="12">
         <v>41</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="9">
         <v>13.666666666666666</v>
       </c>
     </row>
@@ -983,40 +980,40 @@
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>457</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="10">
         <v>173</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="13">
         <v>976</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="7">
         <v>2.1356673960612693</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="10">
         <v>410</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="14">
         <v>494</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="15">
         <v>2029</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="8">
         <v>4.9487804878048784</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="10">
         <v>76</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="11">
         <v>4</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="12">
         <v>39</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="9">
         <v>0.51315789473684215</v>
       </c>
     </row>
@@ -1024,40 +1021,40 @@
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="10">
         <v>222</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="10">
         <v>1</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="13">
         <v>91</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="7">
         <v>0.40990990990990989</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="10">
         <v>263</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="15">
         <v>166</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="8">
         <v>0.63117870722433456</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="10">
         <v>4</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="11">
         <v>0</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="12">
         <v>10</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="9">
         <v>2.5</v>
       </c>
     </row>
@@ -1065,40 +1062,40 @@
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>287</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="10">
         <v>158</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="13">
         <v>659</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="7">
         <v>2.2961672473867596</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="10">
         <v>340</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="14">
         <v>85</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="15">
         <v>653</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="8">
         <v>1.9205882352941177</v>
       </c>
-      <c r="J12" s="14">
-        <v>41</v>
-      </c>
-      <c r="K12" s="15">
+      <c r="J12" s="10">
+        <v>0</v>
+      </c>
+      <c r="K12" s="11">
         <v>18</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="12">
         <v>65</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="9">
         <v>1.5853658536585367</v>
       </c>
     </row>
@@ -1106,40 +1103,40 @@
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="10">
         <v>2967</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="10">
         <v>190</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="13">
         <v>2018</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>0.68014829794405118</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="10">
         <v>1226</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="14">
         <v>46</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="15">
         <v>1903</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="8">
         <v>1.5522022838499185</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="10">
         <v>237</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="11">
         <v>4</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="12">
         <v>133</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="9">
         <v>0.56118143459915615</v>
       </c>
     </row>
@@ -1147,40 +1144,40 @@
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <v>121</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="10">
         <v>156</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="13">
         <v>200</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <v>1.6528925619834711</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="10">
         <v>123</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="14">
         <v>51</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="15">
         <v>185</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="8">
         <v>1.5040650406504066</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="10">
         <v>12</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="11">
         <v>0</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="12">
         <v>16</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="9">
         <v>1.3333333333333333</v>
       </c>
     </row>
@@ -1188,40 +1185,40 @@
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="10">
         <v>504</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="10">
         <v>233</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="13">
         <v>513</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>1.0178571428571428</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="10">
         <v>397</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="14">
         <v>158</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="15">
         <v>801</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="8">
         <v>2.0176322418136019</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="10">
         <v>59</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="11">
         <v>47</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="12">
         <v>155</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="9">
         <v>2.6271186440677967</v>
       </c>
     </row>
@@ -1229,40 +1226,40 @@
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="10">
         <v>53</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="10">
         <v>44</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="13">
         <v>637</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="7">
         <v>12.018867924528301</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="10">
         <v>105</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="14">
         <v>8</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="15">
         <v>651</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="8">
         <v>6.2</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="10">
         <v>22</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="11">
         <v>0</v>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="12">
         <v>9</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="9">
         <v>0.40909090909090912</v>
       </c>
     </row>
@@ -1270,40 +1267,40 @@
       <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="10">
         <v>154</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="10">
         <v>76</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="13">
         <v>253</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="7">
         <v>1.6428571428571428</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="10">
         <v>190</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="14">
         <v>41</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="15">
         <v>252</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="8">
         <v>1.3263157894736841</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="10">
         <v>23</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="11">
         <v>1</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="12">
         <v>37</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="9">
         <v>1.6086956521739131</v>
       </c>
     </row>
@@ -1311,40 +1308,40 @@
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="10">
         <v>355</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="10">
         <v>99</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="13">
         <v>410</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="7">
         <v>1.1549295774647887</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="10">
         <v>176</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="14">
         <v>6</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="15">
         <v>154</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="8">
         <v>0.875</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="10">
         <v>30</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="11">
         <v>2</v>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="12">
         <v>14</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="9">
         <v>0.46666666666666667</v>
       </c>
     </row>
@@ -1352,40 +1349,40 @@
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="10">
         <v>47</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="10">
         <v>3</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="13">
         <v>433</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="7">
         <v>9.212765957446809</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="10">
         <v>35</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="14">
         <v>5</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="15">
         <v>321</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="8">
         <v>9.1714285714285708</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="10">
         <v>2</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="11">
         <v>6</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="12">
         <v>72</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="9">
         <v>36</v>
       </c>
     </row>
@@ -1393,40 +1390,40 @@
       <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="10">
         <v>965</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="10">
         <v>4</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="13">
         <v>70</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="7">
         <v>7.2538860103626937E-2</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="10">
         <v>241</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="14">
         <v>4</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="15">
         <v>194</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="8">
         <v>0.80497925311203322</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="10">
         <v>32</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="11">
         <v>0</v>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="12">
         <v>2</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="9">
         <v>6.25E-2</v>
       </c>
     </row>
@@ -1434,40 +1431,40 @@
       <c r="A21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="10">
         <v>98</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="10">
         <v>14</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="13">
         <v>187</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="7">
         <v>1.9081632653061225</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="10">
         <v>160</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="14">
         <v>19</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="15">
         <v>183</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="8">
         <v>1.14375</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="10">
         <v>3</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="11">
         <v>4</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="12">
         <v>20</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="9">
         <v>6.666666666666667</v>
       </c>
     </row>
@@ -1475,40 +1472,40 @@
       <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="10">
         <v>147</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="10">
         <v>25</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="13">
         <v>263</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="7">
         <v>1.7891156462585034</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="10">
         <v>73</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="14">
         <v>4</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="15">
         <v>136</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="8">
         <v>1.8630136986301369</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="10">
         <v>10</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="11">
         <v>1</v>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="12">
         <v>29</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="9">
         <v>2.9</v>
       </c>
     </row>
@@ -1516,40 +1513,40 @@
       <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="10">
         <v>291</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="10">
         <v>29</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="13">
         <v>205</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="7">
         <v>0.70446735395189009</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="10">
         <v>211</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="14">
         <v>20</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="15">
         <v>189</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="8">
         <v>0.89573459715639814</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="10">
         <v>32</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="11">
         <v>5</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="12">
         <v>43</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="9">
         <v>1.34375</v>
       </c>
     </row>
@@ -1557,40 +1554,40 @@
       <c r="A24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="10">
         <v>369</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="10">
         <v>21</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="13">
         <v>195</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="7">
         <v>0.52845528455284552</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="10">
         <v>175</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="14">
         <v>4</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="15">
         <v>141</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="8">
         <v>0.80571428571428572</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="10">
         <v>22</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="11">
         <v>3</v>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="12">
         <v>21</v>
       </c>
-      <c r="M24" s="13">
+      <c r="M24" s="9">
         <v>0.95454545454545459</v>
       </c>
     </row>
@@ -1598,40 +1595,40 @@
       <c r="A25" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="10">
         <v>261</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="10">
         <v>27</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="13">
         <v>200</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="7">
         <v>0.76628352490421459</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="10">
         <v>306</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="14">
         <v>9</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="15">
         <v>302</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="8">
         <v>0.98692810457516345</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="10">
         <v>18</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="11">
         <v>3</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="12">
         <v>52</v>
       </c>
-      <c r="M25" s="13">
+      <c r="M25" s="9">
         <v>2.8888888888888888</v>
       </c>
     </row>
@@ -1639,40 +1636,40 @@
       <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="10">
         <v>168</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="10">
         <v>13</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="13">
         <v>185</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="7">
         <v>1.1011904761904763</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="10">
         <v>172</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="14">
         <v>3</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="15">
         <v>252</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="8">
         <v>1.4651162790697674</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="10">
         <v>31</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="11">
         <v>0</v>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="12">
         <v>14</v>
       </c>
-      <c r="M26" s="13">
+      <c r="M26" s="9">
         <v>0.45161290322580644</v>
       </c>
     </row>
@@ -1680,40 +1677,40 @@
       <c r="A27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="10">
         <v>1951</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="10">
         <v>2</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="13">
         <v>1994</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="7">
         <v>1.0220399794976935</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="10">
         <v>1908</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="14">
         <v>0</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="15">
         <v>1917</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="8">
         <v>1.0047169811320755</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="10">
         <v>463</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="11">
         <v>1</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="12">
         <v>559</v>
       </c>
-      <c r="M27" s="13">
+      <c r="M27" s="9">
         <v>1.2073434125269979</v>
       </c>
     </row>
@@ -1721,40 +1718,40 @@
       <c r="A28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="10">
         <v>125</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="10">
         <v>15</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="13">
         <v>169</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="7">
         <v>1.3520000000000001</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="10">
         <v>210</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="15">
         <v>238</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="8">
         <v>1.1333333333333333</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="10">
         <v>17</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="11">
         <v>3</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="12">
         <v>24</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="9">
         <v>1.411764705882353</v>
       </c>
     </row>
@@ -1762,40 +1759,40 @@
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="10">
         <v>80</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="10">
         <v>25</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="13">
         <v>147</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="7">
         <v>1.8374999999999999</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="10">
         <v>126</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="14">
         <v>22</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="15">
         <v>296</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="8">
         <v>2.3492063492063493</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="10">
         <v>2</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="11">
         <v>11</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="12">
         <v>116</v>
       </c>
-      <c r="M29" s="13">
+      <c r="M29" s="9">
         <v>58</v>
       </c>
     </row>
@@ -1803,40 +1800,40 @@
       <c r="A30" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="10">
         <v>179</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="10">
         <v>113</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="13">
         <v>741</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="7">
         <v>4.1396648044692741</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="10">
         <v>233</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="14">
         <v>98</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="15">
         <v>740</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="8">
         <v>3.1759656652360513</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="10">
         <v>34</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="11">
         <v>4</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="12">
         <v>27</v>
       </c>
-      <c r="M30" s="13">
+      <c r="M30" s="9">
         <v>0.79411764705882348</v>
       </c>
     </row>
@@ -1844,40 +1841,40 @@
       <c r="A31" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="10">
         <v>235</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="10">
         <v>84</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="13">
         <v>175</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="7">
         <v>0.74468085106382975</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="10">
         <v>173</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="14">
         <v>63</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="15">
         <v>244</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="8">
         <v>1.4104046242774566</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="10">
         <v>5</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="11">
         <v>2</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="12">
         <v>23</v>
       </c>
-      <c r="M31" s="13">
+      <c r="M31" s="9">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -1885,40 +1882,40 @@
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="10">
         <v>121</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="10">
         <v>81</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="13">
         <v>1130</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="7">
         <v>9.338842975206612</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="10">
         <v>293</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="14">
         <v>145</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="15">
         <v>2109</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="8">
         <v>7.197952218430034</v>
       </c>
-      <c r="J32" s="14">
+      <c r="J32" s="10">
         <v>27</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="11">
         <v>64</v>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="12">
         <v>397</v>
       </c>
-      <c r="M32" s="13">
+      <c r="M32" s="9">
         <v>14.703703703703704</v>
       </c>
     </row>
@@ -1926,40 +1923,40 @@
       <c r="A33" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="10">
         <v>96</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="10">
         <v>8</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="13">
         <v>381</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="7">
         <v>3.96875</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="10">
         <v>57</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="14">
         <v>60</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="15">
         <v>331</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="8">
         <v>5.807017543859649</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="10">
         <v>2</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="11">
         <v>4</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="12">
         <v>51</v>
       </c>
-      <c r="M33" s="13">
+      <c r="M33" s="9">
         <v>25.5</v>
       </c>
     </row>
@@ -1967,40 +1964,40 @@
       <c r="A34" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="10">
         <v>120</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="10">
         <v>11</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="13">
         <v>96</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="7">
         <v>0.8</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="10">
         <v>123</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="14">
         <v>6</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="15">
         <v>114</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="8">
         <v>0.92682926829268297</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="10">
         <v>2</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="11">
         <v>0</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="12">
         <v>36</v>
       </c>
-      <c r="M34" s="13">
+      <c r="M34" s="9">
         <v>18</v>
       </c>
     </row>
@@ -2008,40 +2005,40 @@
       <c r="A35" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="10">
         <v>179</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="10">
         <v>147</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="13">
         <v>370</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="7">
         <v>2.0670391061452515</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="10">
         <v>179</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="14">
         <v>41</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="15">
         <v>271</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="8">
         <v>1.5139664804469273</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="10">
         <v>20</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="11">
         <v>6</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="12">
         <v>43</v>
       </c>
-      <c r="M35" s="13">
+      <c r="M35" s="9">
         <v>2.15</v>
       </c>
     </row>

--- a/tinh.xlsx
+++ b/tinh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43A3F9D-5001-4FB6-8744-5D7792910F53}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F401246-40E6-48B5-8F4A-F59C0D84E81D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B4F58B4-2F58-4950-9789-4E40BB9171AB}"/>
+    <workbookView xWindow="22932" yWindow="-84" windowWidth="23256" windowHeight="12456" xr2:uid="{0B4F58B4-2F58-4950-9789-4E40BB9171AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -264,15 +264,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -288,6 +279,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -606,6 +606,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE9B4E2-6DF9-468B-8FA3-042E701409E9}">
   <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -652,163 +657,163 @@
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="7">
         <v>426</v>
       </c>
-      <c r="C2" s="10">
-        <v>78</v>
-      </c>
-      <c r="D2" s="13">
-        <v>413</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0.96948356807511737</v>
-      </c>
-      <c r="F2" s="10">
+      <c r="C2" s="7">
+        <v>87</v>
+      </c>
+      <c r="D2" s="10">
+        <v>500</v>
+      </c>
+      <c r="E2" s="13">
+        <v>1.1737089201877935</v>
+      </c>
+      <c r="F2" s="7">
         <v>330</v>
       </c>
-      <c r="G2" s="14">
-        <v>22</v>
-      </c>
-      <c r="H2" s="15">
-        <v>273</v>
-      </c>
-      <c r="I2" s="8">
-        <v>0.82727272727272727</v>
-      </c>
-      <c r="J2" s="10">
+      <c r="G2" s="11">
+        <v>19</v>
+      </c>
+      <c r="H2" s="12">
+        <v>292</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0.88484848484848488</v>
+      </c>
+      <c r="J2" s="7">
         <v>62</v>
       </c>
-      <c r="K2" s="11">
-        <v>5</v>
-      </c>
-      <c r="L2" s="12">
-        <v>22</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0.35483870967741937</v>
+      <c r="K2" s="8">
+        <v>4</v>
+      </c>
+      <c r="L2" s="9">
+        <v>26</v>
+      </c>
+      <c r="M2" s="15">
+        <v>0.41935483870967744</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>378</v>
       </c>
-      <c r="C3" s="10">
-        <v>38</v>
-      </c>
-      <c r="D3" s="13">
-        <v>153</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0.40476190476190477</v>
-      </c>
-      <c r="F3" s="10">
+      <c r="C3" s="7">
+        <v>35</v>
+      </c>
+      <c r="D3" s="10">
+        <v>188</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0.49735449735449733</v>
+      </c>
+      <c r="F3" s="7">
         <v>342</v>
       </c>
-      <c r="G3" s="14">
-        <v>13</v>
-      </c>
-      <c r="H3" s="15">
-        <v>111</v>
-      </c>
-      <c r="I3" s="8">
-        <v>0.32456140350877194</v>
-      </c>
-      <c r="J3" s="10">
+      <c r="G3" s="11">
+        <v>19</v>
+      </c>
+      <c r="H3" s="12">
+        <v>130</v>
+      </c>
+      <c r="I3" s="14">
+        <v>0.38011695906432746</v>
+      </c>
+      <c r="J3" s="7">
         <v>61</v>
       </c>
-      <c r="K3" s="11">
-        <v>3</v>
-      </c>
-      <c r="L3" s="12">
-        <v>5</v>
-      </c>
-      <c r="M3" s="9">
-        <v>8.1967213114754092E-2</v>
+      <c r="K3" s="8">
+        <v>11</v>
+      </c>
+      <c r="L3" s="9">
+        <v>16</v>
+      </c>
+      <c r="M3" s="15">
+        <v>0.26229508196721313</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>188</v>
       </c>
-      <c r="C4" s="10">
-        <v>91</v>
-      </c>
-      <c r="D4" s="13">
-        <v>359</v>
-      </c>
-      <c r="E4" s="7">
-        <v>1.9095744680851063</v>
-      </c>
-      <c r="F4" s="10">
+      <c r="C4" s="7">
+        <v>82</v>
+      </c>
+      <c r="D4" s="10">
+        <v>441</v>
+      </c>
+      <c r="E4" s="13">
+        <v>2.3457446808510638</v>
+      </c>
+      <c r="F4" s="7">
         <v>200</v>
       </c>
-      <c r="G4" s="14">
-        <v>65</v>
-      </c>
-      <c r="H4" s="15">
-        <v>201</v>
-      </c>
-      <c r="I4" s="8">
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="J4" s="10">
+      <c r="G4" s="11">
+        <v>64</v>
+      </c>
+      <c r="H4" s="12">
+        <v>265</v>
+      </c>
+      <c r="I4" s="14">
+        <v>1.325</v>
+      </c>
+      <c r="J4" s="7">
         <v>17</v>
       </c>
-      <c r="K4" s="11">
-        <v>2</v>
-      </c>
-      <c r="L4" s="12">
-        <v>4</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0.23529411764705882</v>
+      <c r="K4" s="8">
+        <v>1</v>
+      </c>
+      <c r="L4" s="9">
+        <v>5</v>
+      </c>
+      <c r="M4" s="15">
+        <v>0.29411764705882354</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>473</v>
       </c>
-      <c r="C5" s="10">
-        <v>13</v>
-      </c>
-      <c r="D5" s="13">
-        <v>129</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="C5" s="7">
+        <v>27</v>
+      </c>
+      <c r="D5" s="10">
+        <v>156</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0.32980972515856238</v>
+      </c>
+      <c r="F5" s="7">
         <v>307</v>
       </c>
-      <c r="G5" s="14">
-        <v>13</v>
-      </c>
-      <c r="H5" s="15">
-        <v>138</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0.44951140065146578</v>
-      </c>
-      <c r="J5" s="10">
+      <c r="G5" s="11">
+        <v>28</v>
+      </c>
+      <c r="H5" s="12">
+        <v>166</v>
+      </c>
+      <c r="I5" s="14">
+        <v>0.54071661237785018</v>
+      </c>
+      <c r="J5" s="7">
         <v>26</v>
       </c>
-      <c r="K5" s="11">
-        <v>1</v>
-      </c>
-      <c r="L5" s="12">
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
         <v>29</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="15">
         <v>1.1153846153846154</v>
       </c>
     </row>
@@ -816,40 +821,40 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>80</v>
       </c>
-      <c r="C6" s="10">
-        <v>96</v>
-      </c>
-      <c r="D6" s="13">
-        <v>600</v>
-      </c>
-      <c r="E6" s="7">
-        <v>7.5</v>
-      </c>
-      <c r="F6" s="10">
+      <c r="C6" s="7">
+        <v>162</v>
+      </c>
+      <c r="D6" s="10">
+        <v>762</v>
+      </c>
+      <c r="E6" s="13">
+        <v>9.5250000000000004</v>
+      </c>
+      <c r="F6" s="7">
         <v>77</v>
       </c>
-      <c r="G6" s="14">
-        <v>27</v>
-      </c>
-      <c r="H6" s="15">
-        <v>244</v>
-      </c>
-      <c r="I6" s="8">
-        <v>3.168831168831169</v>
-      </c>
-      <c r="J6" s="10">
+      <c r="G6" s="11">
+        <v>33</v>
+      </c>
+      <c r="H6" s="12">
+        <v>277</v>
+      </c>
+      <c r="I6" s="14">
+        <v>3.5974025974025974</v>
+      </c>
+      <c r="J6" s="7">
         <v>2</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="8">
         <v>0</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="9">
         <v>1</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="15">
         <v>0.5</v>
       </c>
     </row>
@@ -857,204 +862,204 @@
       <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>430</v>
       </c>
-      <c r="C7" s="10">
-        <v>116</v>
-      </c>
-      <c r="D7" s="13">
-        <v>1356</v>
-      </c>
-      <c r="E7" s="7">
-        <v>3.1534883720930234</v>
-      </c>
-      <c r="F7" s="10">
+      <c r="C7" s="7">
+        <v>141</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1497</v>
+      </c>
+      <c r="E7" s="13">
+        <v>3.4813953488372094</v>
+      </c>
+      <c r="F7" s="7">
         <v>351</v>
       </c>
-      <c r="G7" s="14">
-        <v>187</v>
-      </c>
-      <c r="H7" s="15">
-        <v>1879</v>
-      </c>
-      <c r="I7" s="8">
-        <v>5.3532763532763532</v>
-      </c>
-      <c r="J7" s="10">
+      <c r="G7" s="11">
+        <v>283</v>
+      </c>
+      <c r="H7" s="12">
+        <v>2162</v>
+      </c>
+      <c r="I7" s="14">
+        <v>6.1595441595441596</v>
+      </c>
+      <c r="J7" s="7">
         <v>59</v>
       </c>
-      <c r="K7" s="11">
-        <v>50</v>
-      </c>
-      <c r="L7" s="12">
-        <v>306</v>
-      </c>
-      <c r="M7" s="9">
-        <v>5.1864406779661021</v>
+      <c r="K7" s="8">
+        <v>42</v>
+      </c>
+      <c r="L7" s="9">
+        <v>348</v>
+      </c>
+      <c r="M7" s="15">
+        <v>5.898305084745763</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>182</v>
       </c>
-      <c r="C8" s="10">
-        <v>10</v>
-      </c>
-      <c r="D8" s="13">
-        <v>167</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.91758241758241754</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="C8" s="7">
+        <v>112</v>
+      </c>
+      <c r="D8" s="10">
+        <v>279</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1.5329670329670331</v>
+      </c>
+      <c r="F8" s="7">
         <v>180</v>
       </c>
-      <c r="G8" s="14">
-        <v>19</v>
-      </c>
-      <c r="H8" s="15">
-        <v>325</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1.8055555555555556</v>
-      </c>
-      <c r="J8" s="10">
+      <c r="G8" s="11">
+        <v>149</v>
+      </c>
+      <c r="H8" s="12">
+        <v>474</v>
+      </c>
+      <c r="I8" s="14">
+        <v>2.6333333333333333</v>
+      </c>
+      <c r="J8" s="7">
         <v>40</v>
       </c>
-      <c r="K8" s="11">
-        <v>1</v>
-      </c>
-      <c r="L8" s="12">
-        <v>31</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0.77500000000000002</v>
+      <c r="K8" s="8">
+        <v>2</v>
+      </c>
+      <c r="L8" s="9">
+        <v>33</v>
+      </c>
+      <c r="M8" s="15">
+        <v>0.82499999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>66</v>
       </c>
-      <c r="C9" s="10">
-        <v>12</v>
-      </c>
-      <c r="D9" s="13">
-        <v>119</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.803030303030303</v>
-      </c>
-      <c r="F9" s="10">
+      <c r="C9" s="7">
+        <v>16</v>
+      </c>
+      <c r="D9" s="10">
+        <v>135</v>
+      </c>
+      <c r="E9" s="13">
+        <v>2.0454545454545454</v>
+      </c>
+      <c r="F9" s="7">
         <v>90</v>
       </c>
-      <c r="G9" s="14">
-        <v>8</v>
-      </c>
-      <c r="H9" s="15">
-        <v>273</v>
-      </c>
-      <c r="I9" s="8">
-        <v>3.0333333333333332</v>
-      </c>
-      <c r="J9" s="10">
+      <c r="G9" s="11">
+        <v>18</v>
+      </c>
+      <c r="H9" s="12">
+        <v>291</v>
+      </c>
+      <c r="I9" s="14">
+        <v>3.2333333333333334</v>
+      </c>
+      <c r="J9" s="7">
         <v>3</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="8">
         <v>4</v>
       </c>
-      <c r="L9" s="12">
-        <v>41</v>
-      </c>
-      <c r="M9" s="9">
-        <v>13.666666666666666</v>
+      <c r="L9" s="9">
+        <v>45</v>
+      </c>
+      <c r="M9" s="15">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>457</v>
       </c>
-      <c r="C10" s="10">
-        <v>173</v>
-      </c>
-      <c r="D10" s="13">
-        <v>976</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.1356673960612693</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="C10" s="7">
+        <v>161</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1137</v>
+      </c>
+      <c r="E10" s="13">
+        <v>2.4879649890590811</v>
+      </c>
+      <c r="F10" s="7">
         <v>410</v>
       </c>
-      <c r="G10" s="14">
-        <v>494</v>
-      </c>
-      <c r="H10" s="15">
-        <v>2029</v>
-      </c>
-      <c r="I10" s="8">
-        <v>4.9487804878048784</v>
-      </c>
-      <c r="J10" s="10">
+      <c r="G10" s="11">
+        <v>590</v>
+      </c>
+      <c r="H10" s="12">
+        <v>2619</v>
+      </c>
+      <c r="I10" s="14">
+        <v>6.3878048780487804</v>
+      </c>
+      <c r="J10" s="7">
         <v>76</v>
       </c>
-      <c r="K10" s="11">
-        <v>4</v>
-      </c>
-      <c r="L10" s="12">
-        <v>39</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0.51315789473684215</v>
+      <c r="K10" s="8">
+        <v>11</v>
+      </c>
+      <c r="L10" s="9">
+        <v>50</v>
+      </c>
+      <c r="M10" s="15">
+        <v>0.65789473684210531</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>222</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="7">
         <v>1</v>
       </c>
-      <c r="D11" s="13">
-        <v>91</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.40990990990990989</v>
-      </c>
-      <c r="F11" s="10">
+      <c r="D11" s="10">
+        <v>92</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.4144144144144144</v>
+      </c>
+      <c r="F11" s="7">
         <v>263</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="11">
+        <v>9</v>
+      </c>
+      <c r="H11" s="12">
+        <v>175</v>
+      </c>
+      <c r="I11" s="14">
+        <v>0.66539923954372626</v>
+      </c>
+      <c r="J11" s="7">
+        <v>4</v>
+      </c>
+      <c r="K11" s="8">
         <v>0</v>
       </c>
-      <c r="H11" s="15">
-        <v>166</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0.63117870722433456</v>
-      </c>
-      <c r="J11" s="10">
-        <v>4</v>
-      </c>
-      <c r="K11" s="11">
-        <v>0</v>
-      </c>
-      <c r="L11" s="12">
+      <c r="L11" s="9">
         <v>10</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="15">
         <v>2.5</v>
       </c>
     </row>
@@ -1062,204 +1067,204 @@
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>287</v>
       </c>
-      <c r="C12" s="10">
-        <v>158</v>
-      </c>
-      <c r="D12" s="13">
-        <v>659</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.2961672473867596</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="C12" s="7">
+        <v>265</v>
+      </c>
+      <c r="D12" s="10">
+        <v>924</v>
+      </c>
+      <c r="E12" s="13">
+        <v>3.2195121951219514</v>
+      </c>
+      <c r="F12" s="7">
         <v>340</v>
       </c>
-      <c r="G12" s="14">
-        <v>85</v>
-      </c>
-      <c r="H12" s="15">
-        <v>653</v>
-      </c>
-      <c r="I12" s="8">
-        <v>1.9205882352941177</v>
-      </c>
-      <c r="J12" s="10">
-        <v>0</v>
-      </c>
-      <c r="K12" s="11">
-        <v>18</v>
-      </c>
-      <c r="L12" s="12">
-        <v>65</v>
-      </c>
-      <c r="M12" s="9">
-        <v>1.5853658536585367</v>
+      <c r="G12" s="11">
+        <v>127</v>
+      </c>
+      <c r="H12" s="12">
+        <v>780</v>
+      </c>
+      <c r="I12" s="14">
+        <v>2.2941176470588234</v>
+      </c>
+      <c r="J12" s="7">
+        <v>41</v>
+      </c>
+      <c r="K12" s="8">
+        <v>17</v>
+      </c>
+      <c r="L12" s="9">
+        <v>82</v>
+      </c>
+      <c r="M12" s="15">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>2967</v>
       </c>
-      <c r="C13" s="10">
-        <v>190</v>
-      </c>
-      <c r="D13" s="13">
-        <v>2018</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.68014829794405118</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="C13" s="7">
+        <v>276</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2294</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0.77317155375800473</v>
+      </c>
+      <c r="F13" s="7">
         <v>1226</v>
       </c>
-      <c r="G13" s="14">
-        <v>46</v>
-      </c>
-      <c r="H13" s="15">
-        <v>1903</v>
-      </c>
-      <c r="I13" s="8">
-        <v>1.5522022838499185</v>
-      </c>
-      <c r="J13" s="10">
+      <c r="G13" s="11">
+        <v>167</v>
+      </c>
+      <c r="H13" s="12">
+        <v>2070</v>
+      </c>
+      <c r="I13" s="14">
+        <v>1.6884176182707993</v>
+      </c>
+      <c r="J13" s="7">
         <v>237</v>
       </c>
-      <c r="K13" s="11">
-        <v>4</v>
-      </c>
-      <c r="L13" s="12">
-        <v>133</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0.56118143459915615</v>
+      <c r="K13" s="8">
+        <v>19</v>
+      </c>
+      <c r="L13" s="9">
+        <v>152</v>
+      </c>
+      <c r="M13" s="15">
+        <v>0.64135021097046419</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>121</v>
       </c>
-      <c r="C14" s="10">
-        <v>156</v>
-      </c>
-      <c r="D14" s="13">
-        <v>200</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.6528925619834711</v>
-      </c>
-      <c r="F14" s="10">
+      <c r="C14" s="7">
+        <v>99</v>
+      </c>
+      <c r="D14" s="10">
+        <v>299</v>
+      </c>
+      <c r="E14" s="13">
+        <v>2.4710743801652892</v>
+      </c>
+      <c r="F14" s="7">
         <v>123</v>
       </c>
-      <c r="G14" s="14">
-        <v>51</v>
-      </c>
-      <c r="H14" s="15">
-        <v>185</v>
-      </c>
-      <c r="I14" s="8">
-        <v>1.5040650406504066</v>
-      </c>
-      <c r="J14" s="10">
+      <c r="G14" s="11">
+        <v>116</v>
+      </c>
+      <c r="H14" s="12">
+        <v>301</v>
+      </c>
+      <c r="I14" s="14">
+        <v>2.4471544715447155</v>
+      </c>
+      <c r="J14" s="7">
         <v>12</v>
       </c>
-      <c r="K14" s="11">
-        <v>0</v>
-      </c>
-      <c r="L14" s="12">
-        <v>16</v>
-      </c>
-      <c r="M14" s="9">
-        <v>1.3333333333333333</v>
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="9">
+        <v>17</v>
+      </c>
+      <c r="M14" s="15">
+        <v>1.4166666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>504</v>
       </c>
-      <c r="C15" s="10">
-        <v>233</v>
-      </c>
-      <c r="D15" s="13">
-        <v>513</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.0178571428571428</v>
-      </c>
-      <c r="F15" s="10">
+      <c r="C15" s="7">
+        <v>154</v>
+      </c>
+      <c r="D15" s="10">
+        <v>667</v>
+      </c>
+      <c r="E15" s="13">
+        <v>1.3234126984126984</v>
+      </c>
+      <c r="F15" s="7">
         <v>397</v>
       </c>
-      <c r="G15" s="14">
-        <v>158</v>
-      </c>
-      <c r="H15" s="15">
-        <v>801</v>
-      </c>
-      <c r="I15" s="8">
-        <v>2.0176322418136019</v>
-      </c>
-      <c r="J15" s="10">
+      <c r="G15" s="11">
+        <v>254</v>
+      </c>
+      <c r="H15" s="12">
+        <v>1055</v>
+      </c>
+      <c r="I15" s="14">
+        <v>2.6574307304785894</v>
+      </c>
+      <c r="J15" s="7">
         <v>59</v>
       </c>
-      <c r="K15" s="11">
-        <v>47</v>
-      </c>
-      <c r="L15" s="12">
-        <v>155</v>
-      </c>
-      <c r="M15" s="9">
-        <v>2.6271186440677967</v>
+      <c r="K15" s="8">
+        <v>83</v>
+      </c>
+      <c r="L15" s="9">
+        <v>238</v>
+      </c>
+      <c r="M15" s="15">
+        <v>4.0338983050847457</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>53</v>
       </c>
-      <c r="C16" s="10">
-        <v>44</v>
-      </c>
-      <c r="D16" s="13">
-        <v>637</v>
-      </c>
-      <c r="E16" s="7">
-        <v>12.018867924528301</v>
-      </c>
-      <c r="F16" s="10">
+      <c r="C16" s="7">
+        <v>67</v>
+      </c>
+      <c r="D16" s="10">
+        <v>704</v>
+      </c>
+      <c r="E16" s="13">
+        <v>13.283018867924529</v>
+      </c>
+      <c r="F16" s="7">
         <v>105</v>
       </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
-      <c r="H16" s="15">
-        <v>651</v>
-      </c>
-      <c r="I16" s="8">
-        <v>6.2</v>
-      </c>
-      <c r="J16" s="10">
+      <c r="G16" s="11">
+        <v>10</v>
+      </c>
+      <c r="H16" s="12">
+        <v>661</v>
+      </c>
+      <c r="I16" s="14">
+        <v>6.2952380952380951</v>
+      </c>
+      <c r="J16" s="7">
         <v>22</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="8">
         <v>0</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="9">
         <v>9</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="15">
         <v>0.40909090909090912</v>
       </c>
     </row>
@@ -1267,81 +1272,81 @@
       <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>154</v>
       </c>
-      <c r="C17" s="10">
-        <v>76</v>
-      </c>
-      <c r="D17" s="13">
-        <v>253</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.6428571428571428</v>
-      </c>
-      <c r="F17" s="10">
+      <c r="C17" s="7">
+        <v>71</v>
+      </c>
+      <c r="D17" s="10">
+        <v>324</v>
+      </c>
+      <c r="E17" s="13">
+        <v>2.1038961038961039</v>
+      </c>
+      <c r="F17" s="7">
         <v>190</v>
       </c>
-      <c r="G17" s="14">
-        <v>41</v>
-      </c>
-      <c r="H17" s="15">
-        <v>252</v>
-      </c>
-      <c r="I17" s="8">
-        <v>1.3263157894736841</v>
-      </c>
-      <c r="J17" s="10">
+      <c r="G17" s="11">
+        <v>37</v>
+      </c>
+      <c r="H17" s="12">
+        <v>289</v>
+      </c>
+      <c r="I17" s="14">
+        <v>1.5210526315789474</v>
+      </c>
+      <c r="J17" s="7">
         <v>23</v>
       </c>
-      <c r="K17" s="11">
-        <v>1</v>
-      </c>
-      <c r="L17" s="12">
-        <v>37</v>
-      </c>
-      <c r="M17" s="9">
-        <v>1.6086956521739131</v>
+      <c r="K17" s="8">
+        <v>7</v>
+      </c>
+      <c r="L17" s="9">
+        <v>44</v>
+      </c>
+      <c r="M17" s="15">
+        <v>1.9130434782608696</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="7">
         <v>355</v>
       </c>
-      <c r="C18" s="10">
-        <v>99</v>
-      </c>
-      <c r="D18" s="13">
-        <v>410</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.1549295774647887</v>
-      </c>
-      <c r="F18" s="10">
+      <c r="C18" s="7">
+        <v>15</v>
+      </c>
+      <c r="D18" s="10">
+        <v>425</v>
+      </c>
+      <c r="E18" s="13">
+        <v>1.1971830985915493</v>
+      </c>
+      <c r="F18" s="7">
         <v>176</v>
       </c>
-      <c r="G18" s="14">
-        <v>6</v>
-      </c>
-      <c r="H18" s="15">
-        <v>154</v>
-      </c>
-      <c r="I18" s="8">
-        <v>0.875</v>
-      </c>
-      <c r="J18" s="10">
+      <c r="G18" s="11">
+        <v>36</v>
+      </c>
+      <c r="H18" s="12">
+        <v>190</v>
+      </c>
+      <c r="I18" s="14">
+        <v>1.0795454545454546</v>
+      </c>
+      <c r="J18" s="7">
         <v>30</v>
       </c>
-      <c r="K18" s="11">
-        <v>2</v>
-      </c>
-      <c r="L18" s="12">
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
         <v>14</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="15">
         <v>0.46666666666666667</v>
       </c>
     </row>
@@ -1349,163 +1354,163 @@
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>47</v>
       </c>
-      <c r="C19" s="10">
-        <v>3</v>
-      </c>
-      <c r="D19" s="13">
-        <v>433</v>
-      </c>
-      <c r="E19" s="7">
-        <v>9.212765957446809</v>
-      </c>
-      <c r="F19" s="10">
+      <c r="C19" s="7">
+        <v>17</v>
+      </c>
+      <c r="D19" s="10">
+        <v>450</v>
+      </c>
+      <c r="E19" s="13">
+        <v>9.5744680851063837</v>
+      </c>
+      <c r="F19" s="7">
         <v>35</v>
       </c>
-      <c r="G19" s="14">
-        <v>5</v>
-      </c>
-      <c r="H19" s="15">
-        <v>321</v>
-      </c>
-      <c r="I19" s="8">
-        <v>9.1714285714285708</v>
-      </c>
-      <c r="J19" s="10">
+      <c r="G19" s="11">
+        <v>14</v>
+      </c>
+      <c r="H19" s="12">
+        <v>335</v>
+      </c>
+      <c r="I19" s="14">
+        <v>9.5714285714285712</v>
+      </c>
+      <c r="J19" s="7">
         <v>2</v>
       </c>
-      <c r="K19" s="11">
-        <v>6</v>
-      </c>
-      <c r="L19" s="12">
-        <v>72</v>
-      </c>
-      <c r="M19" s="9">
-        <v>36</v>
+      <c r="K19" s="8">
+        <v>22</v>
+      </c>
+      <c r="L19" s="9">
+        <v>94</v>
+      </c>
+      <c r="M19" s="15">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>965</v>
       </c>
-      <c r="C20" s="10">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13">
-        <v>70</v>
-      </c>
-      <c r="E20" s="7">
-        <v>7.2538860103626937E-2</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="C20" s="7">
+        <v>6</v>
+      </c>
+      <c r="D20" s="10">
+        <v>76</v>
+      </c>
+      <c r="E20" s="13">
+        <v>7.8756476683937829E-2</v>
+      </c>
+      <c r="F20" s="7">
         <v>241</v>
       </c>
-      <c r="G20" s="14">
-        <v>4</v>
-      </c>
-      <c r="H20" s="15">
-        <v>194</v>
-      </c>
-      <c r="I20" s="8">
-        <v>0.80497925311203322</v>
-      </c>
-      <c r="J20" s="10">
+      <c r="G20" s="11">
+        <v>2</v>
+      </c>
+      <c r="H20" s="12">
+        <v>196</v>
+      </c>
+      <c r="I20" s="14">
+        <v>0.81327800829875518</v>
+      </c>
+      <c r="J20" s="7">
         <v>32</v>
       </c>
-      <c r="K20" s="11">
-        <v>0</v>
-      </c>
-      <c r="L20" s="12">
-        <v>2</v>
-      </c>
-      <c r="M20" s="9">
-        <v>6.25E-2</v>
+      <c r="K20" s="8">
+        <v>1</v>
+      </c>
+      <c r="L20" s="9">
+        <v>3</v>
+      </c>
+      <c r="M20" s="15">
+        <v>9.375E-2</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="7">
         <v>98</v>
       </c>
-      <c r="C21" s="10">
-        <v>14</v>
-      </c>
-      <c r="D21" s="13">
-        <v>187</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.9081632653061225</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="C21" s="7">
+        <v>32</v>
+      </c>
+      <c r="D21" s="10">
+        <v>219</v>
+      </c>
+      <c r="E21" s="13">
+        <v>2.2346938775510203</v>
+      </c>
+      <c r="F21" s="7">
         <v>160</v>
       </c>
-      <c r="G21" s="14">
-        <v>19</v>
-      </c>
-      <c r="H21" s="15">
-        <v>183</v>
-      </c>
-      <c r="I21" s="8">
-        <v>1.14375</v>
-      </c>
-      <c r="J21" s="10">
+      <c r="G21" s="11">
+        <v>42</v>
+      </c>
+      <c r="H21" s="12">
+        <v>225</v>
+      </c>
+      <c r="I21" s="14">
+        <v>1.40625</v>
+      </c>
+      <c r="J21" s="7">
         <v>3</v>
       </c>
-      <c r="K21" s="11">
-        <v>4</v>
-      </c>
-      <c r="L21" s="12">
-        <v>20</v>
-      </c>
-      <c r="M21" s="9">
-        <v>6.666666666666667</v>
+      <c r="K21" s="8">
+        <v>9</v>
+      </c>
+      <c r="L21" s="9">
+        <v>29</v>
+      </c>
+      <c r="M21" s="15">
+        <v>9.6666666666666661</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="7">
         <v>147</v>
       </c>
-      <c r="C22" s="10">
-        <v>25</v>
-      </c>
-      <c r="D22" s="13">
-        <v>263</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.7891156462585034</v>
-      </c>
-      <c r="F22" s="10">
+      <c r="C22" s="7">
+        <v>3</v>
+      </c>
+      <c r="D22" s="10">
+        <v>266</v>
+      </c>
+      <c r="E22" s="13">
+        <v>1.8095238095238095</v>
+      </c>
+      <c r="F22" s="7">
         <v>73</v>
       </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
-      <c r="H22" s="15">
-        <v>136</v>
-      </c>
-      <c r="I22" s="8">
-        <v>1.8630136986301369</v>
-      </c>
-      <c r="J22" s="10">
+      <c r="G22" s="11">
         <v>10</v>
       </c>
-      <c r="K22" s="11">
-        <v>1</v>
-      </c>
-      <c r="L22" s="12">
+      <c r="H22" s="12">
+        <v>146</v>
+      </c>
+      <c r="I22" s="14">
+        <v>2</v>
+      </c>
+      <c r="J22" s="7">
+        <v>10</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
         <v>29</v>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="15">
         <v>2.9</v>
       </c>
     </row>
@@ -1513,81 +1518,81 @@
       <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="7">
         <v>291</v>
       </c>
-      <c r="C23" s="10">
-        <v>29</v>
-      </c>
-      <c r="D23" s="13">
-        <v>205</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.70446735395189009</v>
-      </c>
-      <c r="F23" s="10">
+      <c r="C23" s="7">
+        <v>64</v>
+      </c>
+      <c r="D23" s="10">
+        <v>269</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0.92439862542955331</v>
+      </c>
+      <c r="F23" s="7">
         <v>211</v>
       </c>
-      <c r="G23" s="14">
-        <v>20</v>
-      </c>
-      <c r="H23" s="15">
-        <v>189</v>
-      </c>
-      <c r="I23" s="8">
-        <v>0.89573459715639814</v>
-      </c>
-      <c r="J23" s="10">
+      <c r="G23" s="11">
+        <v>55</v>
+      </c>
+      <c r="H23" s="12">
+        <v>244</v>
+      </c>
+      <c r="I23" s="14">
+        <v>1.1563981042654028</v>
+      </c>
+      <c r="J23" s="7">
         <v>32</v>
       </c>
-      <c r="K23" s="11">
-        <v>5</v>
-      </c>
-      <c r="L23" s="12">
-        <v>43</v>
-      </c>
-      <c r="M23" s="9">
-        <v>1.34375</v>
+      <c r="K23" s="8">
+        <v>8</v>
+      </c>
+      <c r="L23" s="9">
+        <v>51</v>
+      </c>
+      <c r="M23" s="15">
+        <v>1.59375</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="7">
         <v>369</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="7">
+        <v>11</v>
+      </c>
+      <c r="D24" s="10">
+        <v>206</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0.5582655826558266</v>
+      </c>
+      <c r="F24" s="7">
+        <v>175</v>
+      </c>
+      <c r="G24" s="11">
+        <v>8</v>
+      </c>
+      <c r="H24" s="12">
+        <v>149</v>
+      </c>
+      <c r="I24" s="14">
+        <v>0.85142857142857142</v>
+      </c>
+      <c r="J24" s="7">
+        <v>22</v>
+      </c>
+      <c r="K24" s="8">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
         <v>21</v>
       </c>
-      <c r="D24" s="13">
-        <v>195</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.52845528455284552</v>
-      </c>
-      <c r="F24" s="10">
-        <v>175</v>
-      </c>
-      <c r="G24" s="14">
-        <v>4</v>
-      </c>
-      <c r="H24" s="15">
-        <v>141</v>
-      </c>
-      <c r="I24" s="8">
-        <v>0.80571428571428572</v>
-      </c>
-      <c r="J24" s="10">
-        <v>22</v>
-      </c>
-      <c r="K24" s="11">
-        <v>3</v>
-      </c>
-      <c r="L24" s="12">
-        <v>21</v>
-      </c>
-      <c r="M24" s="9">
+      <c r="M24" s="15">
         <v>0.95454545454545459</v>
       </c>
     </row>
@@ -1595,409 +1600,409 @@
       <c r="A25" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="7">
         <v>261</v>
       </c>
-      <c r="C25" s="10">
-        <v>27</v>
-      </c>
-      <c r="D25" s="13">
-        <v>200</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.76628352490421459</v>
-      </c>
-      <c r="F25" s="10">
+      <c r="C25" s="7">
+        <v>54</v>
+      </c>
+      <c r="D25" s="10">
+        <v>254</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.97318007662835249</v>
+      </c>
+      <c r="F25" s="7">
         <v>306</v>
       </c>
-      <c r="G25" s="14">
-        <v>9</v>
-      </c>
-      <c r="H25" s="15">
-        <v>302</v>
-      </c>
-      <c r="I25" s="8">
-        <v>0.98692810457516345</v>
-      </c>
-      <c r="J25" s="10">
+      <c r="G25" s="11">
+        <v>38</v>
+      </c>
+      <c r="H25" s="12">
+        <v>340</v>
+      </c>
+      <c r="I25" s="14">
+        <v>1.1111111111111112</v>
+      </c>
+      <c r="J25" s="7">
         <v>18</v>
       </c>
-      <c r="K25" s="11">
-        <v>3</v>
-      </c>
-      <c r="L25" s="12">
-        <v>52</v>
-      </c>
-      <c r="M25" s="9">
-        <v>2.8888888888888888</v>
+      <c r="K25" s="8">
+        <v>8</v>
+      </c>
+      <c r="L25" s="9">
+        <v>60</v>
+      </c>
+      <c r="M25" s="15">
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="7">
         <v>168</v>
       </c>
-      <c r="C26" s="10">
-        <v>13</v>
-      </c>
-      <c r="D26" s="13">
-        <v>185</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.1011904761904763</v>
-      </c>
-      <c r="F26" s="10">
+      <c r="C26" s="7">
+        <v>23</v>
+      </c>
+      <c r="D26" s="10">
+        <v>208</v>
+      </c>
+      <c r="E26" s="13">
+        <v>1.2380952380952381</v>
+      </c>
+      <c r="F26" s="7">
         <v>172</v>
       </c>
-      <c r="G26" s="14">
-        <v>3</v>
-      </c>
-      <c r="H26" s="15">
-        <v>252</v>
-      </c>
-      <c r="I26" s="8">
-        <v>1.4651162790697674</v>
-      </c>
-      <c r="J26" s="10">
+      <c r="G26" s="11">
+        <v>1</v>
+      </c>
+      <c r="H26" s="12">
+        <v>253</v>
+      </c>
+      <c r="I26" s="14">
+        <v>1.4709302325581395</v>
+      </c>
+      <c r="J26" s="7">
         <v>31</v>
       </c>
-      <c r="K26" s="11">
-        <v>0</v>
-      </c>
-      <c r="L26" s="12">
-        <v>14</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0.45161290322580644</v>
+      <c r="K26" s="8">
+        <v>1</v>
+      </c>
+      <c r="L26" s="9">
+        <v>15</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0.4838709677419355</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="7">
         <v>1951</v>
       </c>
-      <c r="C27" s="10">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13">
-        <v>1994</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.0220399794976935</v>
-      </c>
-      <c r="F27" s="10">
+      <c r="C27" s="7">
+        <v>7</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2001</v>
+      </c>
+      <c r="E27" s="13">
+        <v>1.0256278831368528</v>
+      </c>
+      <c r="F27" s="7">
         <v>1908</v>
       </c>
-      <c r="G27" s="14">
-        <v>0</v>
-      </c>
-      <c r="H27" s="15">
-        <v>1917</v>
-      </c>
-      <c r="I27" s="8">
-        <v>1.0047169811320755</v>
-      </c>
-      <c r="J27" s="10">
+      <c r="G27" s="11">
+        <v>4</v>
+      </c>
+      <c r="H27" s="12">
+        <v>1921</v>
+      </c>
+      <c r="I27" s="14">
+        <v>1.0068134171907757</v>
+      </c>
+      <c r="J27" s="7">
         <v>463</v>
       </c>
-      <c r="K27" s="11">
-        <v>1</v>
-      </c>
-      <c r="L27" s="12">
-        <v>559</v>
-      </c>
-      <c r="M27" s="9">
-        <v>1.2073434125269979</v>
+      <c r="K27" s="8">
+        <v>3</v>
+      </c>
+      <c r="L27" s="9">
+        <v>562</v>
+      </c>
+      <c r="M27" s="15">
+        <v>1.2138228941684666</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="7">
         <v>125</v>
       </c>
-      <c r="C28" s="10">
-        <v>15</v>
-      </c>
-      <c r="D28" s="13">
-        <v>169</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.3520000000000001</v>
-      </c>
-      <c r="F28" s="10">
+      <c r="C28" s="7">
+        <v>24</v>
+      </c>
+      <c r="D28" s="10">
+        <v>193</v>
+      </c>
+      <c r="E28" s="13">
+        <v>1.544</v>
+      </c>
+      <c r="F28" s="7">
         <v>210</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
-      <c r="H28" s="15">
-        <v>238</v>
-      </c>
-      <c r="I28" s="8">
-        <v>1.1333333333333333</v>
-      </c>
-      <c r="J28" s="10">
+      <c r="G28" s="11">
+        <v>7</v>
+      </c>
+      <c r="H28" s="12">
+        <v>245</v>
+      </c>
+      <c r="I28" s="14">
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="J28" s="7">
         <v>17</v>
       </c>
-      <c r="K28" s="11">
-        <v>3</v>
-      </c>
-      <c r="L28" s="12">
-        <v>24</v>
-      </c>
-      <c r="M28" s="9">
-        <v>1.411764705882353</v>
+      <c r="K28" s="8">
+        <v>4</v>
+      </c>
+      <c r="L28" s="9">
+        <v>28</v>
+      </c>
+      <c r="M28" s="15">
+        <v>1.6470588235294117</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="7">
         <v>80</v>
       </c>
-      <c r="C29" s="10">
-        <v>25</v>
-      </c>
-      <c r="D29" s="13">
-        <v>147</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.8374999999999999</v>
-      </c>
-      <c r="F29" s="10">
+      <c r="C29" s="7">
+        <v>7</v>
+      </c>
+      <c r="D29" s="10">
+        <v>154</v>
+      </c>
+      <c r="E29" s="13">
+        <v>1.925</v>
+      </c>
+      <c r="F29" s="7">
         <v>126</v>
       </c>
-      <c r="G29" s="14">
-        <v>22</v>
-      </c>
-      <c r="H29" s="15">
-        <v>296</v>
-      </c>
-      <c r="I29" s="8">
-        <v>2.3492063492063493</v>
-      </c>
-      <c r="J29" s="10">
+      <c r="G29" s="11">
+        <v>18</v>
+      </c>
+      <c r="H29" s="12">
+        <v>314</v>
+      </c>
+      <c r="I29" s="14">
+        <v>2.4920634920634921</v>
+      </c>
+      <c r="J29" s="7">
         <v>2</v>
       </c>
-      <c r="K29" s="11">
-        <v>11</v>
-      </c>
-      <c r="L29" s="12">
-        <v>116</v>
-      </c>
-      <c r="M29" s="9">
-        <v>58</v>
+      <c r="K29" s="8">
+        <v>7</v>
+      </c>
+      <c r="L29" s="9">
+        <v>123</v>
+      </c>
+      <c r="M29" s="15">
+        <v>61.5</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="7">
         <v>179</v>
       </c>
-      <c r="C30" s="10">
-        <v>113</v>
-      </c>
-      <c r="D30" s="13">
-        <v>741</v>
-      </c>
-      <c r="E30" s="7">
-        <v>4.1396648044692741</v>
-      </c>
-      <c r="F30" s="10">
+      <c r="C30" s="7">
+        <v>43</v>
+      </c>
+      <c r="D30" s="10">
+        <v>784</v>
+      </c>
+      <c r="E30" s="13">
+        <v>4.3798882681564244</v>
+      </c>
+      <c r="F30" s="7">
         <v>233</v>
       </c>
-      <c r="G30" s="14">
-        <v>98</v>
-      </c>
-      <c r="H30" s="15">
-        <v>740</v>
-      </c>
-      <c r="I30" s="8">
-        <v>3.1759656652360513</v>
-      </c>
-      <c r="J30" s="10">
+      <c r="G30" s="11">
+        <v>90</v>
+      </c>
+      <c r="H30" s="12">
+        <v>830</v>
+      </c>
+      <c r="I30" s="14">
+        <v>3.5622317596566524</v>
+      </c>
+      <c r="J30" s="7">
         <v>34</v>
       </c>
-      <c r="K30" s="11">
-        <v>4</v>
-      </c>
-      <c r="L30" s="12">
-        <v>27</v>
-      </c>
-      <c r="M30" s="9">
-        <v>0.79411764705882348</v>
+      <c r="K30" s="8">
+        <v>2</v>
+      </c>
+      <c r="L30" s="9">
+        <v>29</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0.8529411764705882</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="7">
         <v>235</v>
       </c>
-      <c r="C31" s="10">
-        <v>84</v>
-      </c>
-      <c r="D31" s="13">
-        <v>175</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.74468085106382975</v>
-      </c>
-      <c r="F31" s="10">
+      <c r="C31" s="7">
+        <v>104</v>
+      </c>
+      <c r="D31" s="10">
+        <v>279</v>
+      </c>
+      <c r="E31" s="13">
+        <v>1.1872340425531915</v>
+      </c>
+      <c r="F31" s="7">
         <v>173</v>
       </c>
-      <c r="G31" s="14">
-        <v>63</v>
-      </c>
-      <c r="H31" s="15">
-        <v>244</v>
-      </c>
-      <c r="I31" s="8">
-        <v>1.4104046242774566</v>
-      </c>
-      <c r="J31" s="10">
+      <c r="G31" s="11">
+        <v>43</v>
+      </c>
+      <c r="H31" s="12">
+        <v>287</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1.6589595375722543</v>
+      </c>
+      <c r="J31" s="7">
         <v>5</v>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="8">
         <v>2</v>
       </c>
-      <c r="L31" s="12">
-        <v>23</v>
-      </c>
-      <c r="M31" s="9">
-        <v>4.5999999999999996</v>
+      <c r="L31" s="9">
+        <v>25</v>
+      </c>
+      <c r="M31" s="15">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="7">
         <v>121</v>
       </c>
-      <c r="C32" s="10">
-        <v>81</v>
-      </c>
-      <c r="D32" s="13">
-        <v>1130</v>
-      </c>
-      <c r="E32" s="7">
-        <v>9.338842975206612</v>
-      </c>
-      <c r="F32" s="10">
+      <c r="C32" s="7">
+        <v>29</v>
+      </c>
+      <c r="D32" s="10">
+        <v>1159</v>
+      </c>
+      <c r="E32" s="13">
+        <v>9.5785123966942152</v>
+      </c>
+      <c r="F32" s="7">
         <v>293</v>
       </c>
-      <c r="G32" s="14">
-        <v>145</v>
-      </c>
-      <c r="H32" s="15">
-        <v>2109</v>
-      </c>
-      <c r="I32" s="8">
-        <v>7.197952218430034</v>
-      </c>
-      <c r="J32" s="10">
+      <c r="G32" s="11">
+        <v>110</v>
+      </c>
+      <c r="H32" s="12">
+        <v>2219</v>
+      </c>
+      <c r="I32" s="14">
+        <v>7.5733788395904433</v>
+      </c>
+      <c r="J32" s="7">
         <v>27</v>
       </c>
-      <c r="K32" s="11">
-        <v>64</v>
-      </c>
-      <c r="L32" s="12">
-        <v>397</v>
-      </c>
-      <c r="M32" s="9">
-        <v>14.703703703703704</v>
+      <c r="K32" s="8">
+        <v>30</v>
+      </c>
+      <c r="L32" s="9">
+        <v>427</v>
+      </c>
+      <c r="M32" s="15">
+        <v>15.814814814814815</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="7">
         <v>96</v>
       </c>
-      <c r="C33" s="10">
-        <v>8</v>
-      </c>
-      <c r="D33" s="13">
-        <v>381</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3.96875</v>
-      </c>
-      <c r="F33" s="10">
+      <c r="C33" s="7">
+        <v>2</v>
+      </c>
+      <c r="D33" s="10">
+        <v>383</v>
+      </c>
+      <c r="E33" s="13">
+        <v>3.9895833333333335</v>
+      </c>
+      <c r="F33" s="7">
         <v>57</v>
       </c>
-      <c r="G33" s="14">
-        <v>60</v>
-      </c>
-      <c r="H33" s="15">
-        <v>331</v>
-      </c>
-      <c r="I33" s="8">
-        <v>5.807017543859649</v>
-      </c>
-      <c r="J33" s="10">
+      <c r="G33" s="11">
+        <v>3</v>
+      </c>
+      <c r="H33" s="12">
+        <v>334</v>
+      </c>
+      <c r="I33" s="14">
+        <v>5.8596491228070171</v>
+      </c>
+      <c r="J33" s="7">
         <v>2</v>
       </c>
-      <c r="K33" s="11">
-        <v>4</v>
-      </c>
-      <c r="L33" s="12">
-        <v>51</v>
-      </c>
-      <c r="M33" s="9">
-        <v>25.5</v>
+      <c r="K33" s="8">
+        <v>6</v>
+      </c>
+      <c r="L33" s="9">
+        <v>57</v>
+      </c>
+      <c r="M33" s="15">
+        <v>28.5</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="7">
         <v>120</v>
       </c>
-      <c r="C34" s="10">
-        <v>11</v>
-      </c>
-      <c r="D34" s="13">
-        <v>96</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="F34" s="10">
+      <c r="C34" s="7">
+        <v>26</v>
+      </c>
+      <c r="D34" s="10">
+        <v>122</v>
+      </c>
+      <c r="E34" s="13">
+        <v>1.0166666666666666</v>
+      </c>
+      <c r="F34" s="7">
         <v>123</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="11">
         <v>6</v>
       </c>
-      <c r="H34" s="15">
-        <v>114</v>
-      </c>
-      <c r="I34" s="8">
-        <v>0.92682926829268297</v>
-      </c>
-      <c r="J34" s="10">
+      <c r="H34" s="12">
+        <v>120</v>
+      </c>
+      <c r="I34" s="14">
+        <v>0.97560975609756095</v>
+      </c>
+      <c r="J34" s="7">
         <v>2</v>
       </c>
-      <c r="K34" s="11">
+      <c r="K34" s="8">
         <v>0</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="9">
         <v>36</v>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="15">
         <v>18</v>
       </c>
     </row>
@@ -2005,41 +2010,41 @@
       <c r="A35" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="7">
         <v>179</v>
       </c>
-      <c r="C35" s="10">
-        <v>147</v>
-      </c>
-      <c r="D35" s="13">
-        <v>370</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.0670391061452515</v>
-      </c>
-      <c r="F35" s="10">
+      <c r="C35" s="7">
+        <v>65</v>
+      </c>
+      <c r="D35" s="10">
+        <v>435</v>
+      </c>
+      <c r="E35" s="13">
+        <v>2.430167597765363</v>
+      </c>
+      <c r="F35" s="7">
         <v>179</v>
       </c>
-      <c r="G35" s="14">
-        <v>41</v>
-      </c>
-      <c r="H35" s="15">
-        <v>271</v>
-      </c>
-      <c r="I35" s="8">
-        <v>1.5139664804469273</v>
-      </c>
-      <c r="J35" s="10">
+      <c r="G35" s="11">
+        <v>46</v>
+      </c>
+      <c r="H35" s="12">
+        <v>317</v>
+      </c>
+      <c r="I35" s="14">
+        <v>1.770949720670391</v>
+      </c>
+      <c r="J35" s="7">
         <v>20</v>
       </c>
-      <c r="K35" s="11">
-        <v>6</v>
-      </c>
-      <c r="L35" s="12">
-        <v>43</v>
-      </c>
-      <c r="M35" s="9">
-        <v>2.15</v>
+      <c r="K35" s="8">
+        <v>5</v>
+      </c>
+      <c r="L35" s="9">
+        <v>48</v>
+      </c>
+      <c r="M35" s="15">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
